--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6968D2B3-C280-477B-9C06-1E5641B2110B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8443DB-3D53-4B02-B021-1B9ADE04F4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3694,29 +3694,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4127,13 +4127,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4235,22 +4235,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4262,13 +4262,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4288,13 +4288,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4323,13 +4323,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4345,13 +4345,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4415,13 +4415,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4437,7 +4437,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4459,22 +4459,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4535,22 +4535,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4608,22 +4608,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4660,13 +4660,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4789,13 +4789,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4821,13 +4821,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4970,13 +4970,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4989,22 +4989,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5100,13 +5100,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5143,13 +5143,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5157,22 +5157,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5196,6 +5196,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5212,17 +5223,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8443DB-3D53-4B02-B021-1B9ADE04F4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4357AF9-3DE7-45B5-8501-B76D13706EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3694,29 +3694,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4127,13 +4127,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4235,22 +4235,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4262,13 +4262,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4288,13 +4288,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4323,13 +4323,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4345,13 +4345,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4415,13 +4415,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4437,7 +4437,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4459,22 +4459,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4535,22 +4535,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4608,22 +4608,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4660,13 +4660,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4789,13 +4789,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4821,13 +4821,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4970,13 +4970,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4989,22 +4989,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5100,13 +5100,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5143,13 +5143,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5157,22 +5157,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5196,17 +5196,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5223,6 +5212,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4357AF9-3DE7-45B5-8501-B76D13706EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799AE5AD-5024-431A-9382-6CA8F2983DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3694,29 +3694,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4127,13 +4127,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4235,22 +4235,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4262,13 +4262,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4288,13 +4288,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4323,13 +4323,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4345,13 +4345,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4415,13 +4415,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4437,7 +4437,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4459,22 +4459,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4535,22 +4535,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4608,22 +4608,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4660,13 +4660,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4789,13 +4789,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4821,13 +4821,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4970,13 +4970,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4989,22 +4989,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5100,13 +5100,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5143,13 +5143,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5157,22 +5157,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5196,6 +5196,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5212,17 +5223,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799AE5AD-5024-431A-9382-6CA8F2983DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ED2193-4450-4B72-AD19-1331AA454F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1317,10 +1317,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1821,14 +1817,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2314,6 +2302,49 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sirius XM Holdings Inc.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SIRI</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2322,12 +2353,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Sirius XM Holdings Inc.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TMT_05</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
   </si>
 </sst>
 </file>
@@ -3001,7 +3031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3694,29 +3724,32 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4006,7 +4039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4026,15 +4059,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4058,13 +4091,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4108,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4091,7 +4124,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4101,7 +4134,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4127,24 +4160,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>374</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="339" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4154,10 +4187,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4180,18 +4213,23 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4203,7 +4241,7 @@
         <v>16.165402289394244</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4211,7 +4249,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4226,7 +4264,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4235,22 +4273,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>375</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="342" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4262,13 +4300,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="340" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4288,13 +4326,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="340" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4323,13 +4361,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4345,17 +4383,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="340" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4370,7 +4408,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4403,7 +4441,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4415,13 +4453,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4437,13 +4475,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4459,26 +4497,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="339" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4504,7 +4542,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4513,7 +4551,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4522,7 +4560,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4535,22 +4573,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4559,7 +4597,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4567,26 +4605,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4603,27 +4641,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4635,7 +4673,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4648,7 +4686,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4660,13 +4698,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4679,13 +4717,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4702,7 +4740,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4720,7 +4758,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4733,7 +4771,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4746,7 +4784,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4777,7 +4815,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4789,17 +4827,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
@@ -4812,7 +4850,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4821,13 +4859,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>382</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="340" t="s">
+        <v>379</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4970,17 +5008,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>385</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="343" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>372</v>
+        <v>417</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4989,22 +5027,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="344" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>384</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5013,7 +5051,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5022,7 +5060,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5044,7 +5082,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>264</v>
+        <v>414</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5089,124 +5127,160 @@
         <v>0.44846710599062711</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>1.6646413756219209</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>26.474246761493756</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>416</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>28.138888137115678</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>3.9954457635030138E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>388</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>392</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>394</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>395</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>396</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>397</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>398</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5223,9 +5297,20 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B143:F143"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5732,7 +5817,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181">
         <v>1741</v>
@@ -5768,7 +5853,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181">
         <v>-970</v>
@@ -5804,7 +5889,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181">
         <v>-916</v>
@@ -5863,7 +5948,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7132,7 +7217,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8502,13 +8587,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8516,7 +8601,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8669,7 +8754,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>138</v>
@@ -8692,7 +8777,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8714,7 +8799,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -8781,7 +8866,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -8793,7 +8878,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8804,12 +8889,12 @@
         <v>-534.31656312939253</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8820,12 +8905,12 @@
         <v>0.30319105036010147</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8833,12 +8918,12 @@
         <v>534.31656312939253</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8846,7 +8931,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8922,7 +9007,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8933,15 +9018,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8958,7 +9043,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8992,7 +9077,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9863,7 +9948,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9888,7 +9973,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10216,7 +10301,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10276,7 +10361,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10400,7 +10485,7 @@
         <v>-1462.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10458,7 +10543,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10766,7 +10851,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10905,7 +10990,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10960,7 +11045,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11093,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11120,7 +11205,7 @@
         <v>4.7027590784109223E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11435,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11996,7 +12081,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12675,7 +12760,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13369,7 +13454,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13421,7 +13506,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13874,7 +13959,7 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13930,7 +14015,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14759,10 +14844,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14777,8 +14862,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14793,8 +14878,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14809,8 +14894,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14880,7 +14965,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14939,7 +15024,7 @@
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14961,7 +15046,7 @@
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14983,7 +15068,7 @@
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15005,7 +15090,7 @@
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15027,7 +15112,7 @@
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15049,7 +15134,7 @@
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15071,7 +15156,7 @@
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15093,7 +15178,7 @@
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15115,7 +15200,7 @@
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15137,7 +15222,7 @@
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -16155,7 +16240,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16207,7 +16292,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16227,7 +16312,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16281,7 +16366,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16294,7 +16379,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16304,11 +16389,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM Holdings Inc.(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16329,8 +16414,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16351,8 +16436,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16362,8 +16447,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16374,10 +16459,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16395,8 +16480,8 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16413,8 +16498,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16431,8 +16516,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16448,7 +16533,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16458,25 +16543,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16486,12 +16571,12 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16501,8 +16586,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16522,8 +16607,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16533,8 +16618,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16548,8 +16633,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16559,8 +16644,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16580,8 +16665,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16591,8 +16676,8 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16606,8 +16691,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16617,8 +16702,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16638,8 +16723,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16649,8 +16734,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16664,8 +16749,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16676,8 +16761,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16739,8 +16824,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16750,8 +16835,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16765,8 +16850,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16776,12 +16861,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -16797,8 +16882,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16808,8 +16893,8 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16823,8 +16908,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16834,8 +16919,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16850,7 +16935,7 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16859,7 +16944,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16868,10 +16953,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16884,7 +16969,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16892,11 +16977,11 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>1.4959784233939497E-2</v>
+        <v>1.49597842339395E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16912,20 +16997,20 @@
         <v>USD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16935,19 +17020,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16957,14 +17042,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16987,7 +17072,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17010,12 +17095,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -17069,12 +17154,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17087,7 +17172,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17097,43 +17182,99 @@
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>411</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>1.6646413756219209</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>26.474246761493756</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>28.138888137115678</v>
+      </c>
+      <c r="D93" t="s">
+        <v>409</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>3.9954457635030138E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>335</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>336</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>337</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>336</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>337</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>336</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>339</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>337</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>340</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ED2193-4450-4B72-AD19-1331AA454F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BB9C29-B66A-4F1A-A22C-5C58BBDBB980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1353,10 +1353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2313,31 +2309,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3031,7 +3043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3727,6 +3739,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4039,7 +4056,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4059,10 +4076,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4091,13 +4108,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4108,7 +4125,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4124,7 +4141,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4160,24 +4177,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4187,10 +4204,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4213,19 +4230,19 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4237,11 +4254,11 @@
         <v>Target Buy Price (USD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>16.165402289394244</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4249,7 +4266,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4264,7 +4281,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4273,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4300,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4326,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4361,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4383,17 +4400,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4408,7 +4425,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4453,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4475,13 +4492,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>349</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>348</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4497,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>353</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4559,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4551,7 +4568,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4560,7 +4577,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4573,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4597,7 +4614,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4605,26 +4622,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4641,27 +4658,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4673,7 +4690,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4686,7 +4703,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4698,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>376</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4717,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4740,7 +4757,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4751,537 +4768,577 @@
         <v>USD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>417</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>1.4851905363915479</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>418</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>0.95241105291674188</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>4.0148803043206254</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>162</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>-372.31656312939253</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>-1.0993945571003985</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>625.79999999999995</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>1.8478928470188039</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>26.591820192356398</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>370</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>379</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>-38.360607814419353</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>369</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>378</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>5.5E-2</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>45.55 USD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>33.27 USD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>29.32 USD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.01</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>24.88 USD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.05</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>15.12 USD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>29.309951346473134</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>382</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>417</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>415</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>379</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>0.59360000000000002</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>1.1587072</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>15.006695089394245</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>16.165402289394244</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.44846710599062711</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.6646413756219209</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>1.5948076513008855</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>26.474246761493756</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>416</v>
-      </c>
-      <c r="C135" s="239">
+        <v>24.801732327498168</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>414</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>28.138888137115678</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>26.396539978799055</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>3.9954457635030138E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>9.9400075190662185E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>385</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>386</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>391</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>388</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>394</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5290,24 +5347,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5817,7 +5874,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C22" s="181">
         <v>1741</v>
@@ -5853,7 +5910,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C23" s="181">
         <v>-970</v>
@@ -5889,7 +5946,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C24" s="181">
         <v>-916</v>
@@ -5948,7 +6005,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7217,7 +7274,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8593,7 +8650,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>273</v>
+        <v>419</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8601,7 +8658,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8754,7 +8811,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>138</v>
@@ -8777,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8799,7 +8856,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -8866,7 +8923,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -8878,7 +8935,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8889,12 +8946,12 @@
         <v>-534.31656312939253</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8905,12 +8962,12 @@
         <v>0.30319105036010147</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8918,12 +8975,12 @@
         <v>534.31656312939253</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8931,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9007,7 +9064,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9018,15 +9075,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>298</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9043,7 +9100,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9077,7 +9134,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9948,7 +10005,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9973,7 +10030,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10301,7 +10358,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10361,7 +10418,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10485,7 +10542,7 @@
         <v>-1462.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10543,7 +10600,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10851,7 +10908,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10990,7 +11047,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11045,7 +11102,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11178,7 +11235,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11205,7 +11262,7 @@
         <v>4.7027590784109223E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11520,7 +11577,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12081,7 +12138,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12760,7 +12817,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13454,7 +13511,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13506,7 +13563,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14015,7 +14072,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14844,10 +14901,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14862,8 +14919,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14878,8 +14935,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14894,8 +14951,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16240,7 +16297,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16312,7 +16369,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16366,7 +16423,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16379,7 +16436,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16389,11 +16446,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM Holdings Inc.(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16414,8 +16471,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16436,8 +16493,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16447,8 +16504,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16459,10 +16516,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>279</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16480,8 +16537,8 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16498,8 +16555,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16516,8 +16573,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16533,7 +16590,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16543,25 +16600,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>341</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>312</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>311</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16571,12 +16628,12 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16586,8 +16643,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16607,8 +16664,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16618,8 +16675,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16633,8 +16690,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16644,8 +16701,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16665,8 +16722,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16676,8 +16733,8 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16691,8 +16748,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16702,8 +16759,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16723,8 +16780,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16734,8 +16791,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16749,8 +16806,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16761,8 +16818,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16824,8 +16881,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16835,8 +16892,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16850,8 +16907,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16861,12 +16918,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -16882,8 +16939,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16893,8 +16950,8 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16908,8 +16965,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16919,8 +16976,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16935,7 +16992,7 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16944,7 +17001,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16953,10 +17010,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16969,7 +17026,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16981,7 +17038,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16997,20 +17054,20 @@
         <v>USD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17020,19 +17077,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17042,14 +17099,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17072,7 +17129,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17095,15 +17152,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -17154,12 +17211,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17172,7 +17229,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17184,16 +17241,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17202,7 +17259,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.6646413756219209</v>
+        <v>1.5948076513008855</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17212,27 +17269,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>26.474246761493756</v>
+        <v>24.801732327498168</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>28.138888137115678</v>
+        <v>26.396539978799055</v>
       </c>
       <c r="D93" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>3.9954457635030138E-2</v>
+        <v>9.9400075190662185E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17240,7 +17297,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17248,30 +17305,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>335</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>336</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>337</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BB9C29-B66A-4F1A-A22C-5C58BBDBB980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4209A76-68AA-4F1F-B4C1-EEB2FD8D1115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="425">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1410,10 +1410,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3744,29 +3740,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4076,10 +4072,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4108,13 +4104,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>420</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>421</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4125,7 +4121,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4141,7 +4137,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4177,24 +4173,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="342" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="B12" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4204,10 +4200,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4230,7 +4226,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4242,7 +4238,7 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4258,7 +4254,7 @@
         <v>16.165402289394244</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4266,7 +4262,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4281,7 +4277,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4290,22 +4286,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="B25" s="340" t="s">
+        <v>370</v>
+      </c>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="345" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="B26" s="342" t="s">
+        <v>348</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4313,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4339,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4374,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4400,17 +4396,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4425,7 +4421,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4470,13 +4466,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4492,8 +4488,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="343" t="s">
-        <v>348</v>
+      <c r="B50" s="341" t="s">
+        <v>347</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
@@ -4514,22 +4510,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="342" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="B53" s="340" t="s">
+        <v>352</v>
+      </c>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="B54" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4559,7 +4555,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4568,7 +4564,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4577,7 +4573,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4590,22 +4586,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="B63" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4614,7 +4610,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4622,26 +4618,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4658,27 +4654,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4703,7 +4699,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4715,13 +4711,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="B81" s="340" t="s">
+        <v>375</v>
+      </c>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4730,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="B85" s="340" t="s">
+        <v>353</v>
+      </c>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4770,7 +4766,7 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="337" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
@@ -4779,7 +4775,7 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="337" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
@@ -4788,7 +4784,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="337" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
@@ -4871,13 +4867,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="B101" s="340" t="s">
+        <v>376</v>
+      </c>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B103" s="47" t="s">
@@ -4894,7 +4890,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B104" s="337" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4907,7 +4903,7 @@
     </row>
     <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A106" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4916,13 +4912,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="343" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="B108" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B110" s="260" t="s">
@@ -5065,17 +5061,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="346" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="B119" s="345" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A121" s="247" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5084,22 +5080,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
+        <v>378</v>
+      </c>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="340" t="s">
         <v>379</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="342" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B125" s="234" t="s">
@@ -5139,7 +5135,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B130" s="234" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -5186,7 +5182,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -5211,7 +5207,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="80" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
@@ -5233,7 +5229,7 @@
     </row>
     <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A142" s="247" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5242,22 +5238,22 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="B144" s="347" t="s">
+        <v>386</v>
+      </c>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B146" s="234" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B147" s="344" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
@@ -5266,78 +5262,89 @@
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B148" s="238" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="238" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>392</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="B153" s="341" t="s">
+        <v>391</v>
+      </c>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
+        <v>392</v>
+      </c>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="346" t="s">
         <v>393</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B159" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B160" s="238" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="161" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B161" s="238" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B162" s="238" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5354,20 +5361,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5874,7 +5870,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C22" s="181">
         <v>1741</v>
@@ -5910,7 +5906,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C23" s="181">
         <v>-970</v>
@@ -5946,7 +5942,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C24" s="181">
         <v>-916</v>
@@ -6005,7 +6001,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7274,7 +7270,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8650,7 +8646,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8856,7 +8852,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -8923,7 +8919,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -8935,7 +8931,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8946,12 +8942,12 @@
         <v>-534.31656312939253</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8962,12 +8958,12 @@
         <v>0.30319105036010147</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8975,12 +8971,12 @@
         <v>534.31656312939253</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8988,7 +8984,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9064,7 +9060,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9075,15 +9071,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>297</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9100,7 +9096,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9134,7 +9130,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -10005,7 +10001,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10030,7 +10026,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10358,7 +10354,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10418,7 +10414,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10542,7 +10538,7 @@
         <v>-1462.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10600,7 +10596,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10908,7 +10904,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11047,7 +11043,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11102,7 +11098,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11235,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11262,7 +11258,7 @@
         <v>4.7027590784109223E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11577,7 +11573,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12138,7 +12134,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12817,7 +12813,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13511,7 +13507,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13563,7 +13559,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14072,7 +14068,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -16297,7 +16293,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16369,7 +16365,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16590,7 +16586,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16601,7 +16597,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F18" s="351"/>
     </row>
@@ -16611,7 +16607,7 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
@@ -16923,7 +16919,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -16992,7 +16988,7 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -17001,7 +16997,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17010,10 +17006,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -17026,7 +17022,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -17038,7 +17034,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -17054,20 +17050,20 @@
         <v>USD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17077,19 +17073,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17099,14 +17095,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17129,7 +17125,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17152,12 +17148,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
@@ -17211,12 +17207,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17229,7 +17225,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17241,12 +17237,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="135">
         <f>(Thesis!E19+Thesis!C67)/2</f>
@@ -17275,14 +17271,14 @@
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
         <v>26.396539978799055</v>
       </c>
       <c r="D93" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
@@ -17297,7 +17293,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17305,30 +17301,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>334</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>335</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>336</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4209A76-68AA-4F1F-B4C1-EEB2FD8D1115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772C3F13-6EA0-4738-B976-563CA4DBE237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1577,10 +1578,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1785,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2349,23 +2342,34 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>Sirius XM Holdings Inc.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SIRI</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>USD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TMT_05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -2373,26 +2377,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3067,7 +3071,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3109,23 +3113,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3134,13 +3138,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3211,10 +3215,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3225,7 +3229,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3263,7 +3267,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3273,7 +3277,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3284,29 +3288,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3322,7 +3326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3336,38 +3340,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3387,17 +3391,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3412,11 +3416,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3425,51 +3429,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3485,7 +3489,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3519,21 +3523,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3542,7 +3546,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3552,13 +3556,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3569,7 +3573,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3588,9 +3592,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3599,23 +3603,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3633,13 +3637,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3647,7 +3651,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3684,7 +3688,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3706,21 +3710,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3731,7 +3735,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3739,7 +3743,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4053,7 +4057,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4063,7 +4067,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4072,13 +4076,13 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
         <v>268</v>
       </c>
@@ -4092,7 +4096,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>SIRI Stock Information</v>
@@ -4102,18 +4106,18 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>95</v>
       </c>
@@ -4121,11 +4125,11 @@
         <v>20.079999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4135,7 +4139,7 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
         <v>314</v>
       </c>
@@ -4145,7 +4149,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
         <v>269</v>
       </c>
@@ -4156,7 +4160,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (USD):</v>
@@ -4168,29 +4172,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
       <c r="B12" s="340" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C12" s="340"/>
       <c r="D12" s="340"/>
       <c r="E12" s="340"/>
       <c r="F12" s="340"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
         <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4198,17 +4202,17 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
@@ -4221,16 +4225,16 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>277</v>
       </c>
@@ -4238,13 +4242,13 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (USD):</v>
@@ -4260,9 +4264,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4271,13 +4275,13 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4285,34 +4289,34 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
       <c r="B25" s="340" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C25" s="340"/>
       <c r="D25" s="340"/>
       <c r="E25" s="340"/>
       <c r="F25" s="340"/>
     </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
       <c r="B26" s="342" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C26" s="342"/>
       <c r="D26" s="342"/>
       <c r="E26" s="342"/>
       <c r="F26" s="342"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
         <v>231</v>
       </c>
       <c r="C28" s="108">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
       <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
@@ -4321,7 +4325,7 @@
       <c r="E29" s="341"/>
       <c r="F29" s="341"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
         <v>233</v>
       </c>
@@ -4334,11 +4338,11 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
       <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
@@ -4347,7 +4351,7 @@
       <c r="E32" s="341"/>
       <c r="F32" s="341"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
         <v>235</v>
       </c>
@@ -4360,7 +4364,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
         <v>236</v>
       </c>
@@ -4373,7 +4377,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6">
       <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
@@ -4382,7 +4386,7 @@
       <c r="E36" s="341"/>
       <c r="F36" s="341"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
         <v>238</v>
       </c>
@@ -4395,7 +4399,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
@@ -4404,9 +4408,9 @@
       <c r="E39" s="341"/>
       <c r="F39" s="341"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4419,9 +4423,9 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4434,7 +4438,7 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
         <v>239</v>
       </c>
@@ -4447,12 +4451,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
         <v>266</v>
       </c>
@@ -4465,7 +4469,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6">
       <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
@@ -4474,7 +4478,7 @@
       <c r="E47" s="341"/>
       <c r="F47" s="341"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
         <v>240</v>
       </c>
@@ -4487,16 +4491,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6">
       <c r="B50" s="341" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
       <c r="E50" s="344"/>
       <c r="F50" s="344"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
         <v>243</v>
       </c>
@@ -4509,25 +4513,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
       <c r="B53" s="340" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C53" s="340"/>
       <c r="D53" s="340"/>
       <c r="E53" s="340"/>
       <c r="F53" s="340"/>
     </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
       <c r="B54" s="340" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C54" s="340"/>
       <c r="D54" s="340"/>
       <c r="E54" s="340"/>
       <c r="F54" s="340"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
         <v>271</v>
       </c>
@@ -4540,7 +4544,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
         <v>249</v>
       </c>
@@ -4553,16 +4557,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.22703991769612522</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
         <v>316</v>
       </c>
@@ -4571,9 +4575,9 @@
         <v>2.956175298804781E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4581,20 +4585,20 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
       <c r="B63" s="340" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C63" s="340"/>
       <c r="D63" s="340"/>
       <c r="E63" s="340"/>
       <c r="F63" s="340"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6">
       <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
@@ -4603,12 +4607,12 @@
       <c r="E64" s="342"/>
       <c r="F64" s="342"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
         <v>288</v>
       </c>
@@ -4616,7 +4620,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
         <v>290</v>
       </c>
@@ -4625,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
         <v>289</v>
       </c>
@@ -4637,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
         <v>248</v>
       </c>
@@ -4649,34 +4653,34 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
       <c r="B73" s="340" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C73" s="340"/>
       <c r="D73" s="340"/>
       <c r="E73" s="340"/>
       <c r="F73" s="340"/>
     </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="B74" s="340" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C74" s="340"/>
       <c r="D74" s="340"/>
       <c r="E74" s="340"/>
       <c r="F74" s="340"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
         <v>252</v>
       </c>
@@ -4684,12 +4688,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
         <v>284</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>56.987019341727418</v>
       </c>
       <c r="D77" s="1" t="str">
@@ -4697,9 +4701,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4707,38 +4711,38 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6">
       <c r="B81" s="340" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C81" s="340"/>
       <c r="D81" s="340"/>
       <c r="E81" s="340"/>
       <c r="F81" s="340"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
       <c r="B85" s="340" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C85" s="340"/>
       <c r="D85" s="340"/>
       <c r="E85" s="340"/>
       <c r="F85" s="340"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
         <v>256</v>
       </c>
@@ -4751,12 +4755,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
         <v>285</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.143697439289426</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4764,39 +4768,39 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6">
       <c r="B88" s="337" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>1.4851905363915479</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6">
       <c r="B89" s="337" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>0.95241105291674188</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6">
       <c r="B90" s="337" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
         <v>4.0148803043206254</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
         <v>265</v>
       </c>
@@ -4809,7 +4813,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
         <v>267</v>
       </c>
@@ -4822,12 +4826,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
         <v>286</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>-1.0993945571003985</v>
       </c>
       <c r="D95" s="1" t="str">
@@ -4835,12 +4839,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6">
       <c r="B98" s="47" t="s">
         <v>258</v>
       </c>
@@ -4853,12 +4857,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
         <v>287</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.8478928470188039</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -4866,16 +4870,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
       <c r="B101" s="340" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C101" s="340"/>
       <c r="D101" s="340"/>
       <c r="E101" s="340"/>
       <c r="F101" s="340"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
         <v>283</v>
       </c>
@@ -4888,9 +4892,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="B104" s="337" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4901,9 +4905,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4911,16 +4915,16 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
       <c r="B108" s="341" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C108" s="341"/>
       <c r="D108" s="341"/>
       <c r="E108" s="341"/>
       <c r="F108" s="341"/>
     </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
         <v>118</v>
       </c>
@@ -4937,7 +4941,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4959,7 +4963,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4981,7 +4985,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5003,7 +5007,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5025,7 +5029,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5047,7 +5051,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
         <v>259</v>
       </c>
@@ -5060,18 +5064,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
       <c r="B119" s="345" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C119" s="345"/>
       <c r="D119" s="345"/>
       <c r="E119" s="345"/>
       <c r="F119" s="345"/>
     </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5079,30 +5083,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
       <c r="B123" s="343" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C123" s="343"/>
       <c r="D123" s="343"/>
       <c r="E123" s="343"/>
       <c r="F123" s="343"/>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
       <c r="B124" s="340" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C124" s="340"/>
       <c r="D124" s="340"/>
       <c r="E124" s="340"/>
       <c r="F124" s="340"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
         <v>264</v>
       </c>
@@ -5111,7 +5115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
         <v>278</v>
       </c>
@@ -5120,7 +5124,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
         <v>262</v>
       </c>
@@ -5133,12 +5137,19 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5148,7 +5159,7 @@
         <v>1.1587072</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5158,7 +5169,7 @@
         <v>15.006695089394245</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
@@ -5171,7 +5182,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
@@ -5180,56 +5191,63 @@
         <v>0.44846710599062711</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.5948076513008855</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.5866998932004295</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>24.801732327498168</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>24.609200335237418</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>26.396539978799055</v>
+        <v>26.195900228437846</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>9.9400075190662185E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>0.10624552327719927</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5237,99 +5255,99 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6">
       <c r="B144" s="347" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C144" s="340"/>
       <c r="D144" s="340"/>
       <c r="E144" s="340"/>
       <c r="F144" s="340"/>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
       <c r="B147" s="344" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
       <c r="E147" s="344"/>
       <c r="F147" s="344"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
+      <c r="B149" s="238" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
+    <row r="152" spans="2:6">
+      <c r="B152" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="341" t="s">
         <v>389</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="341" t="s">
-        <v>391</v>
       </c>
       <c r="C153" s="341"/>
       <c r="D153" s="341"/>
       <c r="E153" s="341"/>
       <c r="F153" s="341"/>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
       <c r="B156" s="346" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C156" s="346"/>
       <c r="D156" s="346"/>
       <c r="E156" s="346"/>
       <c r="F156" s="346"/>
     </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
       <c r="B157" s="346" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C157" s="346"/>
       <c r="D157" s="346"/>
       <c r="E157" s="346"/>
       <c r="F157" s="346"/>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
       <c r="B160" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="238" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B161" s="238" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B162" s="238" t="s">
-        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -5363,7 +5381,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5385,7 +5403,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5393,7 +5411,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>USD</v>
@@ -5442,7 +5460,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5458,7 +5476,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5466,7 +5484,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5502,7 +5520,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -5538,7 +5556,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -5560,7 +5578,7 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -5582,7 +5600,7 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -5598,7 +5616,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -5614,7 +5632,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -5630,7 +5648,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -5646,7 +5664,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5682,7 +5700,7 @@
       </c>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -5698,7 +5716,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -5734,7 +5752,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -5770,7 +5788,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -5790,13 +5808,13 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -5816,7 +5834,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -5842,7 +5860,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -5868,9 +5886,9 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>1741</v>
@@ -5904,9 +5922,9 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-970</v>
@@ -5940,9 +5958,9 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-916</v>
@@ -5976,7 +5994,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (USD)</v>
@@ -5996,15 +6014,15 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6041,7 +6059,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6060,7 +6078,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6097,7 +6115,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6134,7 +6152,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6153,7 +6171,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6169,12 +6187,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6223,7 +6241,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6272,7 +6290,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6321,7 +6339,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6370,7 +6388,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6419,7 +6437,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -6468,7 +6486,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -6517,7 +6535,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -6566,7 +6584,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -6615,7 +6633,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -6664,7 +6682,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -6713,7 +6731,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -6762,7 +6780,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -6811,12 +6829,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6865,7 +6883,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -6914,12 +6932,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -6968,7 +6986,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7017,7 +7035,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7066,7 +7084,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7115,13 +7133,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7170,7 +7188,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7219,7 +7237,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7268,9 +7286,9 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7317,7 +7335,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7366,12 +7384,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7421,7 +7439,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -7470,7 +7488,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7520,7 +7538,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -7569,7 +7587,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7619,7 +7637,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -7635,13 +7653,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7690,7 +7708,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -7724,7 +7742,7 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -7758,7 +7776,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7807,7 +7825,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7888,7 +7906,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7899,7 +7917,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7911,11 +7929,11 @@
         <v>FY Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -7926,7 +7944,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -7946,7 +7964,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -7967,7 +7985,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7988,7 +8006,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8009,7 +8027,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8030,7 +8048,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8051,7 +8069,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8072,7 +8090,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8084,7 +8102,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8096,7 +8114,7 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8120,12 +8138,12 @@
         <v>145.80000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8145,7 +8163,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8165,7 +8183,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8185,7 +8203,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8205,7 +8223,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8225,7 +8243,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8245,7 +8263,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8265,7 +8283,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8286,7 +8304,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8298,7 +8316,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8311,7 +8329,7 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8335,7 +8353,7 @@
         <v>625.79999999999995</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8352,7 +8370,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8371,7 +8389,7 @@
         <v>-12991.05</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8386,7 +8404,7 @@
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8405,7 +8423,7 @@
         <v>-12991.05</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8421,7 +8439,7 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8438,7 +8456,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8458,7 +8476,7 @@
         <v>3455.9500000000003</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8469,7 +8487,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
@@ -8482,7 +8500,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -8501,7 +8519,7 @@
         <v>2684.3500000000004</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8517,7 +8535,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8533,7 +8551,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8549,7 +8567,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8568,7 +8586,7 @@
         <v>210.9</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -8588,7 +8606,7 @@
         <v>771.59999999999991</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8608,7 +8626,7 @@
         <v>145.79999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8627,7 +8645,7 @@
         <v>625.79999999999995</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -8638,7 +8656,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -8646,13 +8664,13 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -8666,7 +8684,7 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (USD)</v>
@@ -8681,10 +8699,10 @@
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -8697,7 +8715,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -8711,7 +8729,7 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -8722,10 +8740,10 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -8737,7 +8755,7 @@
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -8751,7 +8769,7 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -8765,10 +8783,10 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -8780,7 +8798,7 @@
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -8791,7 +8809,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -8802,10 +8820,10 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -8817,7 +8835,7 @@
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -8833,7 +8851,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -8844,7 +8862,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -8858,7 +8876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -8874,7 +8892,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -8884,7 +8902,7 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -8894,7 +8912,7 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -8904,7 +8922,7 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -8914,10 +8932,10 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
         <v>326</v>
       </c>
@@ -8929,7 +8947,7 @@
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>325</v>
       </c>
@@ -8942,12 +8960,12 @@
         <v>-534.31656312939253</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8961,7 +8979,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>328</v>
       </c>
@@ -8971,12 +8989,12 @@
         <v>534.31656312939253</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8984,13 +9002,13 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9002,7 +9020,7 @@
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9016,7 +9034,7 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9030,7 +9048,7 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9044,7 +9062,7 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9058,7 +9076,7 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>295</v>
       </c>
@@ -9069,7 +9087,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>296</v>
       </c>
@@ -9077,7 +9095,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
         <v>293</v>
       </c>
@@ -9086,7 +9104,7 @@
         <v>-10547</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
+        <f>C86*scaling_factor/Common_Shares</f>
         <v>-31.143697439289426</v>
       </c>
       <c r="E86" s="269" t="str">
@@ -9094,7 +9112,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
         <v>294</v>
       </c>
@@ -9103,7 +9121,7 @@
         <v>-372.31656312939253</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
+        <f>C87*scaling_factor/Common_Shares</f>
         <v>-1.0993945571003985</v>
       </c>
       <c r="E87" s="269" t="str">
@@ -9111,7 +9129,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
         <v>190</v>
       </c>
@@ -9120,7 +9138,7 @@
         <v>625.79999999999995</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
+        <f>C88*scaling_factor/Common_Shares</f>
         <v>1.8478928470188039</v>
       </c>
       <c r="E88" s="269" t="str">
@@ -9128,7 +9146,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>298</v>
       </c>
@@ -9159,7 +9177,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -9171,7 +9189,7 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
@@ -9228,7 +9246,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9251,13 +9269,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
@@ -9265,7 +9283,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9322,7 +9340,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9377,7 +9395,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9432,7 +9450,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -9487,7 +9505,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -9544,7 +9562,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -9599,7 +9617,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -9654,7 +9672,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -9711,7 +9729,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -9766,7 +9784,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -9821,7 +9839,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -9876,7 +9894,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -9933,7 +9951,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -9990,7 +10008,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10001,7 +10019,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10016,7 +10034,7 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10026,7 +10044,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10041,7 +10059,7 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10098,7 +10116,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10117,7 +10135,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10140,7 +10158,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10161,7 +10179,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10218,7 +10236,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10275,7 +10293,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10332,18 +10350,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10354,7 +10372,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10402,7 +10420,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10414,7 +10432,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10462,7 +10480,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -10517,18 +10535,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -10538,7 +10556,7 @@
         <v>-1462.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10585,7 +10603,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -10596,7 +10614,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10644,7 +10662,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -10701,18 +10719,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10770,7 +10788,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10828,7 +10846,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -10883,18 +10901,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -10904,7 +10922,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10952,10 +10970,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -10978,14 +10996,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11040,10 +11058,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11095,10 +11113,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11152,7 +11170,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11207,11 +11225,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11221,7 +11239,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11231,7 +11249,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11248,7 +11266,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11258,7 +11276,7 @@
         <v>4.7027590784109223E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11275,7 +11293,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11330,11 +11348,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11344,7 +11362,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11399,7 +11417,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11454,7 +11472,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -11509,7 +11527,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -11564,7 +11582,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -11573,7 +11591,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11620,7 +11638,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -11675,11 +11693,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -11689,7 +11707,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -11714,7 +11732,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -11739,7 +11757,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -11764,7 +11782,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -11791,10 +11809,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -11802,7 +11820,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>426</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11817,7 +11835,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -11838,7 +11856,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -11895,7 +11913,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -11952,7 +11970,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12009,7 +12027,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12066,7 +12084,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12123,7 +12141,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12134,7 +12152,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>363</v>
+        <v>427</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12182,7 +12200,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12239,7 +12257,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12296,7 +12314,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12353,7 +12371,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12410,7 +12428,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12468,7 +12486,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -12525,7 +12543,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -12551,7 +12569,7 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -12575,7 +12593,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -12632,18 +12650,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12699,19 +12717,19 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (USD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
+        <f>C90*Common_Shares/scaling_factor</f>
         <v>201.02620160000001</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>201.02620160000001</v>
       </c>
       <c r="H91" s="74">
@@ -12755,18 +12773,18 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.130205090311977</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.18613537185185186</v>
       </c>
       <c r="H92" s="171">
@@ -12810,7 +12828,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>317</v>
@@ -12865,11 +12883,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -12890,7 +12908,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -12947,7 +12965,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13004,10 +13022,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13030,7 +13048,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13040,7 +13058,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13097,7 +13115,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13154,7 +13172,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13211,7 +13229,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13268,7 +13286,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13325,11 +13343,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13352,7 +13370,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13409,7 +13427,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -13466,7 +13484,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -13493,21 +13511,21 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13556,10 +13574,10 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13608,11 +13626,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13666,7 +13684,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -13721,7 +13739,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -13775,7 +13793,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -13831,7 +13849,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -13888,7 +13906,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13907,7 +13925,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -13930,7 +13948,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -13951,7 +13969,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14009,7 +14027,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14066,9 +14084,9 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14116,688 +14134,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14819,7 +14837,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
@@ -14828,7 +14846,7 @@
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -14840,12 +14858,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
       <c r="C3" s="107">
-        <f>Normalized_FCF!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
@@ -14853,7 +14871,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -14874,7 +14892,7 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" s="227" t="s">
         <v>124</v>
       </c>
@@ -14885,7 +14903,7 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
@@ -14903,7 +14921,7 @@
       <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -14919,7 +14937,7 @@
       <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -14935,7 +14953,7 @@
       <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" s="227" t="s">
         <v>191</v>
       </c>
@@ -14951,7 +14969,7 @@
       <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
@@ -14965,7 +14983,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="230" t="s">
         <v>167</v>
       </c>
@@ -14979,12 +14997,12 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
-        <f>(C10*C3)/Common_Shares*C11</f>
+        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
         <v>26.591820192356398</v>
       </c>
       <c r="D12" t="str">
@@ -14993,10 +15011,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15006,13 +15024,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15022,7 +15040,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15032,12 +15050,12 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
+        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
         <v>29.310620301790603</v>
       </c>
       <c r="D18" t="str">
@@ -15046,10 +15064,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15067,7 +15085,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15089,7 +15107,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15111,7 +15129,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15133,7 +15151,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15155,7 +15173,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15177,7 +15195,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15199,7 +15217,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15221,7 +15239,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15243,7 +15261,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15265,7 +15283,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15287,7 +15305,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15309,7 +15327,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15331,7 +15349,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15353,7 +15371,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15375,7 +15393,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15397,7 +15415,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15419,7 +15437,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15441,7 +15459,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15463,7 +15481,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15485,7 +15503,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15507,7 +15525,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15529,7 +15547,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -15551,7 +15569,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -15573,7 +15591,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -15595,7 +15613,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -15617,7 +15635,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -15639,7 +15657,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -15661,7 +15679,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -15683,7 +15701,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -15705,7 +15723,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -15727,7 +15745,7 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
@@ -15749,7 +15767,7 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
@@ -15760,11 +15778,11 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -15774,7 +15792,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>20219.733992052592</v>
@@ -15801,7 +15819,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -15823,7 +15841,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -15844,7 +15862,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -15865,7 +15883,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -15886,7 +15904,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -15907,7 +15925,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -15928,14 +15946,14 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -15945,7 +15963,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>-0.05</v>
@@ -15968,7 +15986,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -15994,7 +16012,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16021,7 +16039,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16048,7 +16066,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16075,7 +16093,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16102,7 +16120,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16128,7 +16146,7 @@
         <v>63.645495158457024</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16154,7 +16172,7 @@
         <v>72.679389439430082</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16171,7 +16189,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16193,7 +16211,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16216,7 +16234,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16239,7 +16257,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16262,7 +16280,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16284,14 +16302,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>318</v>
       </c>
@@ -16299,23 +16317,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16346,7 +16364,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I98"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -16356,7 +16374,7 @@
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -16369,7 +16387,7 @@
       </c>
       <c r="I2" s="278"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -16381,7 +16399,7 @@
         <v>-20.079999999999998</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -16401,7 +16419,7 @@
         <v>0.59360000000000002</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9">
       <c r="H5" s="276">
         <v>2</v>
       </c>
@@ -16410,7 +16428,7 @@
         <v>0.59360000000000002</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -16430,7 +16448,7 @@
         <v>29.903551346473133</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -16455,7 +16473,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -16477,7 +16495,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -16499,7 +16517,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9">
       <c r="E10" s="350"/>
       <c r="F10" s="350"/>
       <c r="H10" s="276">
@@ -16510,7 +16528,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
@@ -16524,7 +16542,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -16543,7 +16561,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -16561,7 +16579,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -16572,7 +16590,7 @@
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -16581,15 +16599,15 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -16597,22 +16615,22 @@
         <v>10</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F18" s="351"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="E19" s="351"/>
       <c r="F19" s="351"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>280</v>
       </c>
@@ -16627,7 +16645,7 @@
       <c r="E21" s="351"/>
       <c r="F21" s="351"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>281</v>
       </c>
@@ -16642,7 +16660,7 @@
       <c r="E22" s="351"/>
       <c r="F22" s="351"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -16651,7 +16669,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -16663,7 +16681,7 @@
       <c r="E25" s="349"/>
       <c r="F25" s="349"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -16674,7 +16692,7 @@
       <c r="E26" s="349"/>
       <c r="F26" s="349"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
@@ -16689,7 +16707,7 @@
       <c r="E27" s="349"/>
       <c r="F27" s="349"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -16700,7 +16718,7 @@
       <c r="E28" s="349"/>
       <c r="F28" s="349"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -16709,7 +16727,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -16721,7 +16739,7 @@
       <c r="E31" s="349"/>
       <c r="F31" s="349"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -16732,7 +16750,7 @@
       <c r="E32" s="349"/>
       <c r="F32" s="349"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
@@ -16747,7 +16765,7 @@
       <c r="E33" s="349"/>
       <c r="F33" s="349"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -16758,7 +16776,7 @@
       <c r="E34" s="349"/>
       <c r="F34" s="349"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -16767,7 +16785,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -16779,7 +16797,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -16790,7 +16808,7 @@
       <c r="E38" s="349"/>
       <c r="F38" s="349"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
@@ -16805,7 +16823,7 @@
       <c r="E39" s="349"/>
       <c r="F39" s="349"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -16817,7 +16835,7 @@
       <c r="E40" s="349"/>
       <c r="F40" s="349"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
@@ -16830,7 +16848,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -16839,12 +16857,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -16854,12 +16872,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -16868,7 +16886,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -16880,7 +16898,7 @@
       <c r="E49" s="349"/>
       <c r="F49" s="349"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -16891,7 +16909,7 @@
       <c r="E50" s="349"/>
       <c r="F50" s="349"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
@@ -16906,7 +16924,7 @@
       <c r="E51" s="349"/>
       <c r="F51" s="349"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -16917,7 +16935,7 @@
       <c r="E52" s="349"/>
       <c r="F52" s="349"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>324</v>
       </c>
@@ -16926,7 +16944,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -16938,7 +16956,7 @@
       <c r="E55" s="349"/>
       <c r="F55" s="349"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -16949,7 +16967,7 @@
       <c r="E56" s="349"/>
       <c r="F56" s="349"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
@@ -16964,7 +16982,7 @@
       <c r="E57" s="349"/>
       <c r="F57" s="349"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -16975,7 +16993,7 @@
       <c r="E58" s="349"/>
       <c r="F58" s="349"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
@@ -16995,16 +17013,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>311</v>
       </c>
@@ -17012,7 +17030,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -17022,10 +17040,10 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -17037,7 +17055,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
@@ -17053,15 +17071,15 @@
         <v>321</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>312</v>
       </c>
@@ -17071,7 +17089,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>300</v>
       </c>
@@ -17083,7 +17101,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>299</v>
       </c>
@@ -17093,7 +17111,7 @@
       </c>
       <c r="E71" s="281"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>291</v>
       </c>
@@ -17102,14 +17120,14 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
         <v>-1.0370265985797507</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -17118,12 +17136,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
         <v>304</v>
       </c>
@@ -17133,7 +17151,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -17146,12 +17164,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>306</v>
       </c>
@@ -17160,7 +17178,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
@@ -17172,7 +17190,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
@@ -17182,7 +17200,7 @@
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
@@ -17202,15 +17220,15 @@
         <v>0.44846710599062711</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>307</v>
       </c>
@@ -17223,7 +17241,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>305</v>
       </c>
@@ -17232,99 +17250,99 @@
         <v>0.16060765378265396</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>(Thesis!E19+Thesis!C67)/2</f>
-        <v>5.7250000000000002E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.5948076513008855</v>
+        <v>1.5866998932004295</v>
       </c>
       <c r="D91" s="117"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>24.801732327498168</v>
+        <v>24.609200335237418</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>26.396539978799055</v>
+        <v>26.195900228437846</v>
       </c>
       <c r="D93" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>9.9400075190662185E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+        <v>0.10624552327719927</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="100"/>
     </row>
-    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="14.65">
       <c r="E95" s="320" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="13.9">
       <c r="E96" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>334</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>335</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:8" ht="13.9">
       <c r="E97" s="314" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="98" spans="5:8" ht="13.9">
       <c r="E98" s="315" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772C3F13-6EA0-4738-B976-563CA4DBE237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C80845B-735F-4D4B-B480-47B90188D70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C80845B-735F-4D4B-B480-47B90188D70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA8D233-240E-4677-8D5A-9DD85F8805B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3744,29 +3744,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4177,13 +4177,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4290,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4492,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4663,22 +4663,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4871,13 +4871,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4916,13 +4916,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,13 +5065,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5084,22 +5084,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.5866998932004295</v>
+        <v>1.5297647716303417</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>24.609200335237418</v>
+        <v>23.267184361562904</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>26.195900228437846</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.10624552327719927</v>
+        <v>0.15397508374994073</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5256,13 +5256,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5299,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5313,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,17 +5352,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5379,6 +5368,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17263,8 +17263,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.5866998932004295</v>
+        <v>1.5297647716303417</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>24.609200335237418</v>
+        <v>23.267184361562904</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>26.195900228437846</v>
+        <v>24.796949133193245</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.10624552327719927</v>
+        <v>0.15397508374994073</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA8D233-240E-4677-8D5A-9DD85F8805B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A289885-2767-4154-B976-26B9ED4C90E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3736,37 +3741,37 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4084,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4111,10 +4116,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4125,7 +4130,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4177,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4207,7 +4212,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4230,7 +4235,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4242,10 +4247,10 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4266,7 +4271,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4290,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4629,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4641,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4663,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,28 +4774,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>1.4851905363915479</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.95241105291674188</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>4.0148803043206254</v>
       </c>
@@ -4871,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,8 +4898,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4916,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,17 +5070,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5084,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5139,14 +5144,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
         <v>0.25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5193,14 +5198,14 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5209,7 +5214,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>1.5297647716303417</v>
       </c>
     </row>
@@ -5219,16 +5224,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>23.267184361562904</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>24.796949133193245</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5241,7 +5246,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>0.15397508374994073</v>
       </c>
     </row>
@@ -5256,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,6 +5357,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5368,17 +5384,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -6019,7 +6024,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8664,7 +8669,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11820,7 +11825,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12152,7 +12157,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16363,7 +16368,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17255,16 +17260,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17273,9 +17278,11 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.5297647716303417</v>
+        <v>1.2504074074074074</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17283,69 +17290,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>23.267184361562904</v>
+        <v>16.961777399579361</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>24.796949133193245</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>18.21218480698677</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.15397508374994073</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.37863476497451642</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>1.5297647716303417</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>23.267184361562904</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>24.796949133193245</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>0.15397508374994073</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A289885-2767-4154-B976-26B9ED4C90E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228D90CA-EC91-4DB3-A065-C78BC888BEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3749,29 +3749,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4182,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4244,7 +4244,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>419</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>16.165402289394244</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4295,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4475,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4497,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4595,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4668,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4720,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4876,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4921,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5070,13 +5070,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5089,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>418</v>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.1587072</v>
+        <v>1.0780446062812929</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>15.006695089394245</v>
+        <v>13.34089729015618</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>16.165402289394244</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44846710599062711</v>
+        <v>0.5080530251998352</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5261,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5304,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5318,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5357,17 +5357,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5384,6 +5373,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.1587072</v>
+        <v>1.0780446062812929</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>15.006695089394245</v>
+        <v>13.34089729015618</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>16.165402289394244</v>
+        <v>14.418941896437474</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.44846710599062711</v>
+        <v>0.5080530251998352</v>
       </c>
     </row>
     <row r="84" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228D90CA-EC91-4DB3-A065-C78BC888BEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E24295-6AEA-4BCE-BCB5-680288521E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3749,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4061,7 +4063,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4084,7 +4086,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4116,10 +4118,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4130,7 +4132,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4182,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4212,7 +4214,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4235,7 +4237,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4247,7 +4249,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4295,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4475,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4497,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4595,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4634,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4646,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4668,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4720,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4775,7 +4777,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4784,7 +4786,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4793,7 +4795,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4876,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4899,7 +4901,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4921,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5070,17 +5072,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5089,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5142,19 +5144,19 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5164,7 +5166,7 @@
         <v>1.0780446062812929</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5174,7 +5176,7 @@
         <v>13.34089729015618</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
@@ -5187,7 +5189,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
@@ -5196,167 +5198,232 @@
         <v>0.5080530251998352</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>1.5297647716303417</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>1.2504074074074074</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
+        <f>Scenarios!C92</f>
+        <v>16.961777399579361</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="C139" s="239">
+        <f>Scenarios!C93</f>
+        <v>18.21218480698677</v>
+      </c>
+      <c r="D139" s="47" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.37863476497451642</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>1.5297647716303417</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
         <f>Scenarios!C98</f>
         <v>23.267184361562904</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
-      <c r="B139" s="80" t="s">
-        <v>410</v>
-      </c>
-      <c r="C139" s="239">
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
         <f>Scenarios!C99</f>
         <v>24.796949133193245</v>
       </c>
-      <c r="D139" s="101" t="str">
+      <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
-      <c r="B140" s="238" t="s">
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
         <v>0.15397508374994073</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5373,20 +5440,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -6024,7 +6080,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8669,7 +8725,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11825,7 +11881,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12157,7 +12213,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17260,12 +17316,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17323,7 +17379,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E24295-6AEA-4BCE-BCB5-680288521E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAFAE0D-1713-4711-90E1-71869681FAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3751,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4184,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4297,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4597,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4670,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5072,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5317,13 +5317,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5360,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5374,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,17 +5413,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5440,6 +5429,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAFAE0D-1713-4711-90E1-71869681FAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217E7D62-4A6E-482D-B12C-538D952AAAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3751,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4086,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4118,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4132,7 +4135,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4184,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4214,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4237,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4297,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4597,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4636,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4648,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4670,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5146,7 +5149,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5200,14 +5203,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5261,7 +5264,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5317,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5429,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6080,7 +6083,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11881,7 +11884,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12213,7 +12216,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17316,12 +17319,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217E7D62-4A6E-482D-B12C-538D952AAAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEC6F3A-19EE-45BB-91BD-3C2FDA246F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>20.079999999999998</v>
+        <v>21.47</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>6800.2124799999992</v>
+        <v>7270.9443199999996</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16060765378265396</v>
+        <v>0.13438178033413717</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.22703991769612522</v>
+        <v>0.21234101291747526</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.956175298804781E-2</v>
+        <v>2.7647880763856547E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12899,12 +12899,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.956175298804781E-2</v>
+        <v>2.7647880763856547E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.956175298804781E-2</v>
+        <v>2.7647880763856547E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14098,50 +14098,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.22703991769612522</v>
+        <v>0.21234101291747526</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.15881856679866568</v>
+        <v>0.14853641459325603</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13396640217924485</v>
+        <v>0.12529321638375576</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.50130786501541791</v>
+        <v>0.46885244198926829</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.5404242898010152</v>
+        <v>0.50543641076871848</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.49704329238841671</v>
+        <v>0.46486396419000497</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.54321832014284366</v>
+        <v>0.50804955139582209</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.42165329516291822</v>
+        <v>0.39435482845232406</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.34719885693924674</v>
+        <v>0.3247206822235712</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.34512759813058086</v>
+        <v>0.32278351981658426</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.3008069241977569</v>
+        <v>0.28133223278486064</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14155,43 +14155,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.30513752417336232</v>
+        <v>-0.28538246322315391</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18499421947474209</v>
+        <v>0.17301741625770006</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17837677919146436</v>
+        <v>0.16682839898298107</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19322925627170995</v>
+        <v>0.18071930442179482</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9264103935764082E-2</v>
+        <v>1.8016916955293092E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13440756486479671</v>
+        <v>0.12570581753540372</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17292003793387353</v>
+        <v>0.16172493533824778</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5277611090175837E-2</v>
+        <v>8.9109195653969742E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10969260184058251</v>
+        <v>0.10259093828406597</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4957069576743585E-2</v>
+        <v>7.0104236474197071E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16460,7 +16460,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-20.079999999999998</v>
+        <v>-21.47</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>20.079999999999998</v>
+        <v>21.47</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>20.079999999999998</v>
+        <v>21.47</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16060765378265396</v>
+        <v>0.13438178033413717</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEC6F3A-19EE-45BB-91BD-3C2FDA246F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287E6FBD-4756-4F36-81C6-DE74F224CC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>21.47</v>
+        <v>21.15</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>7270.9443199999996</v>
+        <v>7162.5743999999986</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13438178033413717</v>
+        <v>0.14021163259405034</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.21234101291747526</v>
+        <v>0.21555373746279879</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.7647880763856547E-2</v>
+        <v>2.8066193853427897E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12899,12 +12899,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.7647880763856547E-2</v>
+        <v>2.8066193853427897E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.7647880763856547E-2</v>
+        <v>2.8066193853427897E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14098,50 +14098,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.21234101291747526</v>
+        <v>0.21555373746279879</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14853641459325603</v>
+        <v>0.15078377405755117</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12529321638375576</v>
+        <v>0.12718890570965657</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.46885244198926829</v>
+        <v>0.47594619052054804</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.50543641076871848</v>
+        <v>0.51308367561250046</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.46486396419000497</v>
+        <v>0.47189736695789158</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.50804955139582209</v>
+        <v>0.51573635311906851</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.39435482845232406</v>
+        <v>0.40032142632961693</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.3247206822235712</v>
+        <v>0.32963371382222573</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.32278351981658426</v>
+        <v>0.32766724210222525</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.28133223278486064</v>
+        <v>0.28558879611777582</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14155,43 +14155,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.28538246322315391</v>
+        <v>-0.28970030663835061</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17301741625770006</v>
+        <v>0.17563517385592534</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16682839898298107</v>
+        <v>0.16935251660352738</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18071930442179482</v>
+        <v>0.1834535917700206</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8016916955293092E-2</v>
+        <v>1.8289513334758523E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12570581753540372</v>
+        <v>0.12760774952648313</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16172493533824778</v>
+        <v>0.16417183743320002</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9109195653969742E-2</v>
+        <v>9.0457419890814683E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10259093828406597</v>
+        <v>0.10414314160562159</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0104236474197071E-2</v>
+        <v>7.1164915229362233E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16460,7 +16460,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-21.47</v>
+        <v>-21.15</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>21.47</v>
+        <v>21.15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>21.47</v>
+        <v>21.15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13438178033413717</v>
+        <v>0.14021163259405034</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287E6FBD-4756-4F36-81C6-DE74F224CC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFD1F41-E91C-4E44-8D12-87DC059646DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>21.15</v>
+        <v>21.72</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>7162.5743999999986</v>
+        <v>7355.6083200000003</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14021163259405034</v>
+        <v>0.12990849663525528</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.21555373746279879</v>
+        <v>0.2098969404851839</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.8066193853427897E-2</v>
+        <v>2.7329650092081034E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12899,12 +12899,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.8066193853427897E-2</v>
+        <v>2.7329650092081034E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.8066193853427897E-2</v>
+        <v>2.7329650092081034E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14098,50 +14098,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.21555373746279879</v>
+        <v>0.2098969404851839</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.15078377405755117</v>
+        <v>0.1468267413129469</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12718890570965657</v>
+        <v>0.12385107531119874</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.47594619052054804</v>
+        <v>0.46345588994058889</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.51308367561250046</v>
+        <v>0.49961877252322212</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.47189736695789158</v>
+        <v>0.45951332003496348</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.51573635311906851</v>
+        <v>0.50220183556483877</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.40032142632961693</v>
+        <v>0.38981575353919878</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.32963371382222573</v>
+        <v>0.32098310531031649</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.32766724210222525</v>
+        <v>0.31906823989236022</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.28558879611777582</v>
+        <v>0.2780940625179999</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14155,43 +14155,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.28970030663835061</v>
+        <v>-0.28209767428181931</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17563517385592534</v>
+        <v>0.17102596349230298</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16935251660352738</v>
+        <v>0.16490818260426351</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1834535917700206</v>
+        <v>0.17863920193075208</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8289513334758523E-2</v>
+        <v>1.7809539918514857E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12760774952648313</v>
+        <v>0.12425892737040137</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16417183743320002</v>
+        <v>0.1598634604839862</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0457419890814683E-2</v>
+        <v>8.8083537324619265E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10414314160562159</v>
+        <v>0.10141010335906521</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1164915229362233E-2</v>
+        <v>6.9297327675000506E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16460,7 +16460,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-21.15</v>
+        <v>-21.72</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>21.15</v>
+        <v>21.72</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>21.15</v>
+        <v>21.72</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14021163259405034</v>
+        <v>0.12990849663525528</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFD1F41-E91C-4E44-8D12-87DC059646DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BC9EB9-7ECE-4601-83D0-E06D255BC622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,6 +2358,24 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
@@ -2365,6 +2383,9 @@
   </si>
   <si>
     <t>SIRI</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>USD</t>
@@ -3053,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3754,29 +3775,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4066,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4089,7 +4116,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4107,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>SIRI Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>424</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4121,340 +4147,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>338656000</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>21.72</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>338656000</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (USD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>7355.6083200000003</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>USD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>USD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (USD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>14.418941896437474</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.12990849663525528</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>2626.9774440472893</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>578</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-632.31340126010366</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-496</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-496</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4462,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-496</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-496</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-532.74436101182232</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>1080</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>1080</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>1543.9196817753634</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.2098969404851839</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>2.7329650092081034E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>56.987019341727418</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>10547</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.143697439289426</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>1.4851905363915479</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.95241105291674188</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
         <v>415</v>
       </c>
-      <c r="C90" s="338">
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>4.0148803043206254</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>162</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>-372.31656312939253</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.0993945571003985</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>625.79999999999995</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4869,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8478928470188039</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>-372.31656312939253</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>-1.0993945571003985</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>26.591820192356398</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>625.79999999999995</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>414</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>-38.360607814419353</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.8478928470188039</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>26.591820192356398</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>-38.360607814419353</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
         <v>366</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>5.5E-2</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>45.55 USD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>33.27 USD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>29.32 USD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.01</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>24.88 USD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.05</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>15.12 USD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>29.309951346473134</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>0.59360000000000002</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
         <v>418</v>
       </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>SIRI</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>1.0780446062812929</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>13.34089729015618</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>14.418941896437474</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
         <v>USD</v>
       </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.5080530251998352</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
         <v>421</v>
       </c>
-      <c r="C136" s="337">
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>1.2504074074074074</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>16.961777399579361</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>18.21218480698677</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
         <v>USD</v>
       </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.37863476497451642</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="92">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>1.5297647716303417</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>23.267184361562904</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C145" s="239">
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>24.796949133193245</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
         <v>USD</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>0.15397508374994073</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>389</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>391</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5477,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6083,7 +6206,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9256,7 +9379,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -11884,7 +12007,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12216,7 +12339,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -14951,7 +15074,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -14961,7 +15084,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -14979,10 +15102,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -14997,8 +15120,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15013,8 +15136,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15029,8 +15152,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15056,7 +15179,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>USD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16524,11 +16647,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM Holdings Inc.(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16549,8 +16672,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16571,8 +16694,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16582,8 +16705,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16596,8 +16719,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16615,8 +16738,8 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16633,8 +16756,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16651,8 +16774,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16678,21 +16801,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
+      <c r="E18" s="353" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="351"/>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16706,8 +16829,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16721,8 +16844,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16742,8 +16865,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16753,8 +16876,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16768,8 +16891,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16779,8 +16902,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16800,8 +16923,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16811,8 +16934,8 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16826,8 +16949,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16837,8 +16960,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16858,8 +16981,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16869,8 +16992,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16884,8 +17007,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16896,8 +17019,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -16959,8 +17082,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -16970,8 +17093,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -16985,8 +17108,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -16996,8 +17119,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17017,8 +17140,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17028,8 +17151,8 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17043,8 +17166,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17054,8 +17177,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17073,7 +17196,7 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
@@ -17238,7 +17361,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17327,7 +17450,7 @@
         <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17385,7 +17508,7 @@
         <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BC9EB9-7ECE-4601-83D0-E06D255BC622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D33DDF5-948F-4592-ACF3-F56261E7B1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8586,7 +8586,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>0</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D33DDF5-948F-4592-ACF3-F56261E7B1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D68BA8-6BD0-4E53-AE40-CE44DFEE4C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>21.72</v>
+        <v>21.88</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4226,8 +4226,7 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7355.6083200000003</v>
+        <v>1</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>14.418941896437474</v>
+        <v>11.624652823058726</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4349,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12990849663525528</v>
+        <v>0.12708202937377311</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.2098969404851839</v>
+        <v>0.20836204512514597</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4651,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.7329650092081034E-2</v>
+        <v>2.7129798903107863E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>1.0780446062812929</v>
+        <v>0.94318367346938758</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>13.34089729015618</v>
+        <v>10.681469149589338</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>14.418941896437474</v>
+        <v>11.624652823058726</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5080530251998352</v>
+        <v>0.60338887343606862</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13022,12 +13021,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.7329650092081034E-2</v>
+        <v>2.7129798903107863E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.7329650092081034E-2</v>
+        <v>2.7129798903107863E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14221,50 +14220,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.2098969404851839</v>
+        <v>0.20836204512514597</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1468267413129469</v>
+        <v>0.14575305399073157</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12385107531119874</v>
+        <v>0.12294540017181153</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.46345588994058889</v>
+        <v>0.46006681579111475</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.49961877252322212</v>
+        <v>0.49596525316290607</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.45951332003496348</v>
+        <v>0.45615307637840069</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.50220183556483877</v>
+        <v>0.49852942726089117</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.38981575353919878</v>
+        <v>0.38696518130125218</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.32098310531031649</v>
+        <v>0.31863587967733425</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.31906823989236022</v>
+        <v>0.31673501693153855</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.2780940625179999</v>
+        <v>0.27606046791092131</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14278,43 +14277,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.28209767428181931</v>
+        <v>-0.28003480280626669</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17102596349230298</v>
+        <v>0.1697753165929077</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16490818260426351</v>
+        <v>0.16370227267662721</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17863920193075208</v>
+        <v>0.17733288235539008</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7809539918514857E-2</v>
+        <v>1.7679305622949847E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12425892737040137</v>
+        <v>0.12335026976623024</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1598634604839862</v>
+        <v>0.15869444066326233</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8083537324619265E-2</v>
+        <v>8.743941639354344E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10141010335906521</v>
+        <v>0.10066853039117442</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9297327675000506E-2</v>
+        <v>6.8790583048492282E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16583,7 +16582,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-21.72</v>
+        <v>-21.88</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16823,7 +16822,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>21.72</v>
+        <v>21.88</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17362,7 +17361,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17371,7 +17370,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.0780446062812929</v>
+        <v>0.94318367346938758</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17383,7 +17382,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>13.34089729015618</v>
+        <v>10.681469149589338</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17393,7 +17392,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>14.418941896437474</v>
+        <v>11.624652823058726</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17404,7 +17403,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.5080530251998352</v>
+        <v>0.60338887343606862</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17421,7 +17420,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>21.72</v>
+        <v>21.88</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17434,7 +17433,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12990849663525528</v>
+        <v>0.12708202937377311</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D68BA8-6BD0-4E53-AE40-CE44DFEE4C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37EC679-AEB1-4A2D-8E9D-2479C7B43F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <v>1</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>7409.7932799999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37EC679-AEB1-4A2D-8E9D-2479C7B43F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231281EC-BFC9-47DF-9ED4-371439CE4FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -7380,11 +7380,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-728</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-728</v>
       </c>
       <c r="E62" s="183">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231281EC-BFC9-47DF-9ED4-371439CE4FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7F704A-AB34-49C2-8198-A02635DB16BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7F704A-AB34-49C2-8198-A02635DB16BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C1F094-E0DC-4EA0-B2CB-2C7C54999DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2374,6 +2374,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4194,10 +4206,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4206,7 +4218,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>21.88</v>
+        <v>22.48</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4216,7 +4228,7 @@
         <v>425</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
@@ -4227,7 +4239,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7409.7932799999999</v>
+        <v>7612.9868800000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4294,7 +4306,7 @@
         <v>355</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D22" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4310,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4350,10 +4362,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12708202937377311</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.11672702458118978</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4643,7 +4659,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.20836204512514597</v>
+        <v>0.20280078057554243</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4668,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.7129798903107863E-2</v>
+        <v>2.6405693950177937E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4709,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4721,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5308,7 +5324,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5318,7 +5334,7 @@
         <v>1.2504074074074074</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5328,7 +5344,7 @@
         <v>16.961777399579361</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
@@ -5341,7 +5357,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>425</v>
       </c>
@@ -5354,7 +5370,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
@@ -5363,12 +5379,12 @@
         <v>0.37863476497451642</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5377,7 +5393,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5387,7 +5403,7 @@
         <v>1.5297647716303417</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5397,7 +5413,7 @@
         <v>23.267184361562904</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
@@ -5410,7 +5426,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>425</v>
       </c>
@@ -5423,7 +5439,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
@@ -5432,118 +5448,187 @@
         <v>0.15397508374994073</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>1.4321212155571821</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>21.008212246342826</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>22.440333461900007</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.23439581861974057</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6206,7 +6291,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12007,7 +12092,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12339,7 +12424,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13022,12 +13107,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.7129798903107863E-2</v>
+        <v>2.6405693950177937E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.7129798903107863E-2</v>
+        <v>2.6405693950177937E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14221,50 +14306,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.20836204512514597</v>
+        <v>0.20280078057554243</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14575305399073157</v>
+        <v>0.14186284792336329</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12294540017181153</v>
+        <v>0.11966393931313328</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.46006681579111475</v>
+        <v>0.44778745238031986</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.49596525316290607</v>
+        <v>0.48272774640588895</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.45615307637840069</v>
+        <v>0.4439781722045999</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.49852942726089117</v>
+        <v>0.48522348169342966</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.38696518130125218</v>
+        <v>0.37663692913128993</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.31863587967733425</v>
+        <v>0.31013136331583957</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.31673501693153855</v>
+        <v>0.30828123534083912</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.27606046791092131</v>
+        <v>0.26869230595600346</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14278,43 +14363,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.28003480280626669</v>
+        <v>-0.2725605642972026</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1697753165929077</v>
+        <v>0.16524394693295466</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16370227267662721</v>
+        <v>0.15933299493614786</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17733288235539008</v>
+        <v>0.17259979830675867</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7679305622949847E-2</v>
+        <v>1.7207438035148695E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12335026976623024</v>
+        <v>0.12005800277958709</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15869444066326233</v>
+        <v>0.15445882391958096</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.743941639354344E-2</v>
+        <v>8.5105624141046721E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10066853039117442</v>
+        <v>9.798164790742421E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8790583048492282E-2</v>
+        <v>6.6954535458230033E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16550,7 +16635,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16583,7 +16668,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-21.88</v>
+        <v>-22.48</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16823,7 +16908,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>21.88</v>
+        <v>22.48</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17421,7 +17506,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>21.88</v>
+        <v>22.48</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17434,7 +17519,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12708202937377311</v>
+        <v>0.11672702458118978</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17560,33 +17645,89 @@
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>1.4321212155571821</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>21.008212246342826</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>22.440333461900007</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.23439581861974057</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C1F094-E0DC-4EA0-B2CB-2C7C54999DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02A7994-D67E-48AE-AD8A-8274C5FE3F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2391,9 +2391,6 @@
     <t>N</t>
   </si>
   <si>
-    <t>Sirius XM Holdings Inc.</t>
-  </si>
-  <si>
     <t>SIRI</t>
   </si>
   <si>
@@ -2413,6 +2410,9 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
+  </si>
+  <si>
+    <t>Sirius XM</t>
   </si>
 </sst>
 </file>
@@ -3794,29 +3794,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4159,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4206,10 +4206,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
+        <v>435</v>
+      </c>
+      <c r="D11" s="49" t="s">
         <v>436</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4228,7 +4228,7 @@
         <v>425</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
@@ -4276,13 +4276,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4306,7 +4306,7 @@
         <v>355</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D22" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4322,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4386,22 +4386,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4439,13 +4439,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4474,13 +4474,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4496,13 +4496,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4566,13 +4566,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4588,7 +4588,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4610,22 +4610,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4686,22 +4686,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4759,22 +4759,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4811,13 +4811,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4830,13 +4830,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4967,13 +4967,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -5012,13 +5012,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5161,13 +5161,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5180,22 +5180,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5528,13 +5528,13 @@
       <c r="F167" s="36"/>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+      <c r="B169" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
+      <c r="C169" s="345"/>
+      <c r="D169" s="345"/>
+      <c r="E169" s="345"/>
+      <c r="F169" s="345"/>
     </row>
     <row r="171" spans="1:6">
       <c r="B171" s="234" t="s">
@@ -5571,13 +5571,13 @@
       </c>
     </row>
     <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+      <c r="B178" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
+      <c r="C178" s="346"/>
+      <c r="D178" s="346"/>
+      <c r="E178" s="346"/>
+      <c r="F178" s="346"/>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="1" t="s">
@@ -5585,22 +5585,22 @@
       </c>
     </row>
     <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+      <c r="B181" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
+      <c r="C181" s="343"/>
+      <c r="D181" s="343"/>
+      <c r="E181" s="343"/>
+      <c r="F181" s="343"/>
     </row>
     <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+      <c r="B182" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
+      <c r="C182" s="343"/>
+      <c r="D182" s="343"/>
+      <c r="E182" s="343"/>
+      <c r="F182" s="343"/>
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="1" t="s">
@@ -5624,17 +5624,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5651,6 +5640,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6291,7 +6291,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12092,7 +12092,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="E7" s="353" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM Holdings Inc.(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="353"/>
       <c r="H7" s="276">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02A7994-D67E-48AE-AD8A-8274C5FE3F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA51C0E-A99E-489F-80BF-7A960BB4FFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2379,18 +2356,69 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
   </si>
   <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
+    <t>Sirius XM</t>
+  </si>
+  <si>
     <t>SIRI</t>
   </si>
   <si>
@@ -2410,9 +2438,6 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
-  </si>
-  <si>
-    <t>Sirius XM</t>
   </si>
 </sst>
 </file>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,29 +3803,56 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>434</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>442</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>USD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4271,29 +4307,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D22" s="32" t="str">
+      <c r="C23" s="291" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>448</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>438</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (USD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>11.624652823058726</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (USD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>29.309951346473134</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.11672702458118978</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>SIRI (USD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>11.624652823058726</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>427</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>18.21218480698677</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>24.796949133193245</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>22.440333461900007</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>2626.9774440472893</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>578</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-632.31340126010366</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-496</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-496</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-532.74436101182232</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,20 +4676,16 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="str">
@@ -4609,1059 +4693,1092 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>1080</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-532.74436101182232</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>1543.9196817753634</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>1080</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>1543.9196817753634</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.20280078057554243</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>2.6405693950177937E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>56.987019341727418</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>10547</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.143697439289426</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>1.4851905363915479</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>0.95241105291674188</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>4.0148803043206254</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>162</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>-372.31656312939253</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.0993945571003985</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>625.79999999999995</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.8478928470188039</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>-372.31656312939253</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>-1.0993945571003985</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>26.591820192356398</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>625.79999999999995</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>-38.360607814419353</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.8478928470188039</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>26.591820192356398</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>-38.360607814419353</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>5.5E-2</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>45.55 USD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>33.27 USD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>29.32 USD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.01</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>24.88 USD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.05</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>15.12 USD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>29.309951346473134</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>0.59360000000000002</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>SIRI</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>0.94318367346938758</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>10.681469149589338</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>11.624652823058726</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C140" s="340" t="str">
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.60338887343606862</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>1.2504074074074074</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>16.961777399579361</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>18.21218480698677</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C148" s="340" t="str">
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.37863476497451642</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>1.5297647716303417</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>23.267184361562904</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>24.796949133193245</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C156" s="340" t="str">
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>0.15397508374994073</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>1.4321212155571821</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>21.008212246342826</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>22.440333461900007</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C164" s="340" t="str">
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>0.23439581861974057</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="344" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="345"/>
-      <c r="D169" s="345"/>
-      <c r="E169" s="345"/>
-      <c r="F169" s="345"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="346" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="346"/>
-      <c r="D178" s="346"/>
-      <c r="E178" s="346"/>
-      <c r="F178" s="346"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="343" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="343"/>
-      <c r="D181" s="343"/>
-      <c r="E181" s="343"/>
-      <c r="F181" s="343"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="343" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="343"/>
-      <c r="D182" s="343"/>
-      <c r="E182" s="343"/>
-      <c r="F182" s="343"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5675,17 +5792,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6160,7 +6277,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>1741</v>
@@ -6196,7 +6313,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-970</v>
@@ -6232,7 +6349,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-916</v>
@@ -6291,7 +6408,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7560,7 +7677,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8008,11 +8125,11 @@
         <f t="shared" si="40"/>
         <v>670</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8042,11 +8159,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8178,15 +8295,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8243,7 +8360,7 @@
       <c r="C4" s="19">
         <v>676</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8253,7 +8370,7 @@
       <c r="G4" s="19">
         <v>162</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8264,7 +8381,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8274,7 +8391,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8285,7 +8402,7 @@
       <c r="C6" s="19">
         <v>0</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8295,7 +8412,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8306,7 +8423,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8316,7 +8433,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8327,7 +8444,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8337,7 +8454,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8348,7 +8465,7 @@
       <c r="C9" s="19">
         <v>290</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8358,7 +8475,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8369,10 +8486,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8381,10 +8498,10 @@
       <c r="C11" s="19">
         <v>21</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8442,7 +8559,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8451,7 +8568,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8462,7 +8579,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8471,7 +8588,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8482,7 +8599,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8491,7 +8608,7 @@
       <c r="G17" s="19">
         <v>1043</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8502,7 +8619,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8511,7 +8628,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8522,7 +8639,7 @@
       <c r="C19" s="19">
         <v>2109</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8531,7 +8648,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8542,7 +8659,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8551,7 +8668,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8563,7 +8680,7 @@
         <f>8610+1579</f>
         <v>10189</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.2</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8572,7 +8689,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8583,10 +8700,10 @@
       <c r="C22" s="19">
         <v>0</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8596,10 +8713,10 @@
         <f>12390+641</f>
         <v>13031</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8932,13 +9049,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8954,7 +9071,7 @@
         <f>H29</f>
         <v>-12991.05</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -8969,23 +9086,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-38.360607814419353</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -8999,7 +9116,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>5.4478305785123968</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9010,22 +9127,22 @@
         <f>G29/G32</f>
         <v>0.40238363431561353</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9039,7 +9156,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>7.3567411460708318E-2</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9053,22 +9170,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9090,22 +9207,22 @@
         <f>G39/G32</f>
         <v>7.6632389811416735E-2</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9119,7 +9236,7 @@
         <f>G28/G29</f>
         <v>0</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9138,13 +9255,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9172,7 +9289,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9182,7 +9299,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9192,7 +9309,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9202,26 +9319,26 @@
         <f>SUM(C66:C69)</f>
         <v>162</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9232,65 +9349,65 @@
         <v>-534.31656312939253</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>0.27914886356305812</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>0.30319105036010147</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>534.31656312939253</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9304,7 +9421,7 @@
         <f>G7*H7+G17*H17</f>
         <v>625.79999999999995</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9318,7 +9435,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9332,7 +9449,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9346,11 +9463,11 @@
         <f>SUM(D79:D81)</f>
         <v>625.79999999999995</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9361,15 +9478,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9379,14 +9496,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-31.143697439289426</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9396,13 +9513,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>-1.0993945571003985</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9413,24 +9530,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.8478928470188039</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-10293.516563129393</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>-30.395199149371017</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
@@ -9449,22 +9566,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9551,7 +9668,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9565,7 +9682,7 @@
         <v>8837.75</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9621,7 +9738,7 @@
         <f>C25</f>
         <v>-4748.2725559527107</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5392</v>
@@ -9676,7 +9793,7 @@
         <f>C4+C5</f>
         <v>4089.4774440472893</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>3307</v>
@@ -9731,7 +9848,7 @@
         <f>C35</f>
         <v>-1462.5</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1371</v>
@@ -9787,7 +9904,7 @@
         <v>2626.9774440472893</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9843,7 +9960,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>578</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>578</v>
@@ -9898,7 +10015,7 @@
         <f>-C4*C78</f>
         <v>-632.31340126010366</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-728</v>
@@ -9954,7 +10071,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10010,7 +10127,7 @@
         <f>C50</f>
         <v>-496</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-496</v>
@@ -10065,7 +10182,7 @@
         <f>SUM(C8:C12)</f>
         <v>2076.6640427871857</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1290</v>
@@ -10120,7 +10237,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-532.74436101182232</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-210</v>
@@ -10176,7 +10293,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10233,7 +10350,7 @@
         <v>1543.9196817753634</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10290,8 +10407,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10315,8 +10432,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10341,7 +10458,7 @@
         <v>1543.9196817753634</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10437,7 +10554,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10461,7 +10578,7 @@
         <v>-4109.1377805440734</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10518,7 +10635,7 @@
         <v>-639.13477540863767</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10575,7 +10692,7 @@
         <v>-4748.2725559527107</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10624,14 +10741,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10643,8 +10760,8 @@
         <v>0.46495293265187104</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10703,8 +10820,8 @@
         <v>7.2318720874502862E-2</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10761,7 +10878,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.53727165352637385</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.61984136107598575</v>
@@ -10809,14 +10926,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10827,8 +10944,8 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-1462.5</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10885,8 +11002,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10944,7 +11061,7 @@
         <v>-1462.5</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -10993,14 +11110,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11013,7 +11130,7 @@
         <v>0.16548329608780515</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11071,7 +11188,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11127,7 +11244,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.16548329608780515</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.15760432233590069</v>
@@ -11175,26 +11292,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11273,7 +11390,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11284,7 +11401,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-496</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-496</v>
@@ -11333,111 +11450,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328">
+      <c r="P48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324">
+      <c r="P49" s="320">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11451,7 +11568,7 @@
         <f>C47+C48</f>
         <v>-496</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-496</v>
@@ -11499,14 +11616,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11520,8 +11637,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11547,8 +11664,8 @@
         <f>G54</f>
         <v>4.7027590784109223E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11574,7 +11691,7 @@
         <f>-C8/C47</f>
         <v>5.2963254920308254</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>3.903225806451613</v>
@@ -11622,14 +11739,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11643,7 +11760,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11698,7 +11815,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11753,7 +11870,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11808,7 +11925,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11859,11 +11976,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11919,7 +12036,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-3305</v>
@@ -11967,14 +12084,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -11988,7 +12105,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12013,7 +12130,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12038,7 +12155,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12064,7 +12181,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12092,7 +12209,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12114,7 +12231,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12138,7 +12255,7 @@
         <v>0.53727165352637385</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12195,7 +12312,7 @@
         <v>0.46272834647362615</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12252,7 +12369,7 @@
         <v>0.16548329608780515</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12309,7 +12426,7 @@
         <v>0.297245050385821</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12366,7 +12483,7 @@
         <v>6.5401261633334276E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12423,8 +12540,8 @@
         <v>7.1546875761376333E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>441</v>
+      <c r="E78" s="296" t="s">
+        <v>452</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12482,7 +12599,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12539,7 +12656,7 @@
         <v>5.6122881955248789E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12596,7 +12713,7 @@
         <v>0.23497655430253014</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12653,7 +12770,7 @@
         <v>6.0280542107643047E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12706,12 +12823,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12768,7 +12885,7 @@
         <v>0.17469601219488709</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12820,26 +12937,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12849,7 +12966,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12875,7 +12992,7 @@
         <v>0.17469601219488709</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12924,14 +13041,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -12943,7 +13060,7 @@
         <f>G90</f>
         <v>0.59360000000000002</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.59360000000000002</v>
@@ -12999,7 +13116,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>201.02620160000001</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>201.02620160000001</v>
@@ -13054,7 +13171,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.130205090311977</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.18613537185185186</v>
@@ -13103,13 +13220,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>2.6405693950177937E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>2.6405693950177937E-2</v>
@@ -13157,7 +13274,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13166,7 +13283,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13190,7 +13307,7 @@
         <v>1.5950109207955032E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13247,7 +13364,7 @@
         <v>0.60981708743192686</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13325,7 +13442,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13340,7 +13457,7 @@
         <v>27521</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13397,7 +13514,7 @@
         <v>676</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13454,7 +13571,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13511,7 +13628,7 @@
         <v>16447</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13568,7 +13685,7 @@
         <v>11074</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13617,7 +13734,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13626,7 +13743,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13652,7 +13769,7 @@
         <v>7.649005685836327E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13709,7 +13826,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13766,7 +13883,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13785,63 +13902,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>-0.83903614457831321</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4705882352941178</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.6290189612530914</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.5205479452054795</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>15.404580152671755</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.2067833698030634</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.5991403979783874</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.8639698846132475</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>2.3048142393485742</v>
       </c>
-      <c r="P113" s="334">
+      <c r="P113" s="329">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>2.4406365013222842</v>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13849,58 +13966,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.6120370370370369</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>2.030735455543359</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.57964212378996771</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>0.54367346938775507</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.59704142011834316</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>0.54602057390362746</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.65580755908279886</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.78592484792628292</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.73254376654547337</v>
       </c>
-      <c r="P114" s="334">
+      <c r="P114" s="329">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.60817403232674216</v>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13909,7 +14026,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -13965,7 +14082,7 @@
         <f>C81</f>
         <v>0.23497655430253014</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.14829290723071617</v>
@@ -14019,7 +14136,7 @@
         <f>C4/C101</f>
         <v>0.32112750263435197</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.31608589804149556</v>
@@ -14074,7 +14191,7 @@
         <v>2.4851905363915479</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14131,7 +14248,7 @@
         <v>0.23722028571855602</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14227,7 +14344,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14252,7 +14369,7 @@
         <v>4.5589615473381944</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14309,7 +14426,7 @@
         <v>0.20280078057554243</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14358,7 +14475,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15109,13 +15226,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15159,7 +15276,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15169,7 +15286,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15187,10 +15304,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15205,8 +15322,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15221,8 +15338,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15237,8 +15354,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15302,7 +15419,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15312,7 +15429,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15322,7 +15439,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16583,7 +16700,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16636,12 +16753,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16654,19 +16771,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-22.48</v>
       </c>
@@ -16683,19 +16800,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.59360000000000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>0.59360000000000002</v>
       </c>
@@ -16709,13 +16826,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>29.903551346473133</v>
       </c>
@@ -16732,15 +16849,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16757,12 +16874,12 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16779,37 +16896,37 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16823,12 +16940,12 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16841,12 +16958,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16859,8 +16976,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16876,7 +16993,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16886,25 +17003,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16914,12 +17031,12 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16929,8 +17046,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16950,8 +17067,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16961,8 +17078,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16976,8 +17093,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16987,8 +17104,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17008,8 +17125,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17019,8 +17136,8 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17034,8 +17151,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17045,8 +17162,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17066,8 +17183,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17077,8 +17194,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17092,8 +17209,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17104,8 +17221,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17167,8 +17284,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17178,8 +17295,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17193,8 +17310,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17204,12 +17321,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17225,8 +17342,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17236,8 +17353,8 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17251,8 +17368,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17262,8 +17379,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17278,16 +17395,16 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17296,10 +17413,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17311,8 +17428,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17323,8 +17440,8 @@
         <v>1.49597842339395E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17339,23 +17456,23 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17363,38 +17480,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>-1.0370265985797507</v>
       </c>
@@ -17414,10 +17531,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17438,15 +17555,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17487,7 +17604,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.60338887343606862</v>
       </c>
@@ -17497,14 +17614,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>22.48</v>
       </c>
@@ -17515,9 +17632,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.11672702458118978</v>
       </c>
@@ -17527,15 +17644,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17576,28 +17693,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.37863476497451642</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17609,7 +17726,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17621,23 +17738,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>24.796949133193245</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>0.15397508374994073</v>
       </c>
@@ -17647,15 +17764,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17681,19 +17798,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>22.440333461900007</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>0.23439581861974057</v>
       </c>
@@ -17702,33 +17819,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA51C0E-A99E-489F-80BF-7A960BB4FFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F5E823-607C-4AE4-93A1-5F4DFB35C8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,29 +3830,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4254,7 +4254,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.48</v>
+        <v>22.73</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7612.9868800000004</v>
+        <v>7697.6508800000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4312,13 +4312,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11672702458118978</v>
+        <v>0.11252225662960313</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>18.21218480698677</v>
+        <v>17.461949215913869</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4458,7 +4458,7 @@
         <v>440</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4514,22 +4514,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4541,13 +4541,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4567,13 +4567,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4602,13 +4602,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4738,22 +4738,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.20280078057554243</v>
+        <v>0.20057023965412205</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.6405693950177937E-2</v>
+        <v>2.6115266168059832E-2</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4814,22 +4814,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4873,22 +4873,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4944,13 +4944,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5081,13 +5081,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5126,13 +5126,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5275,13 +5275,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,22 +5294,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>1.2504074074074074</v>
+        <v>1.2171179290462264</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>16.961777399579361</v>
+        <v>16.244831286867644</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>18.21218480698677</v>
+        <v>17.461949215913869</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37863476497451642</v>
+        <v>0.40423138170732364</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5642,13 +5642,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5685,13 +5685,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5699,22 +5699,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,17 +5738,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5765,6 +5754,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.6405693950177937E-2</v>
+        <v>2.6115266168059832E-2</v>
       </c>
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.6405693950177937E-2</v>
+        <v>2.6115266168059832E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14423,50 +14423,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.20280078057554243</v>
+        <v>0.20057023965412205</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14186284792336329</v>
+        <v>0.14030254383269716</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11966393931313328</v>
+        <v>0.11834779391813621</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.44778745238031986</v>
+        <v>0.44286238141265244</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.48272774640588895</v>
+        <v>0.47741837831959455</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.4439781722045999</v>
+        <v>0.4390949982912189</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.48522348169342966</v>
+        <v>0.47988666381294759</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.37663692913128993</v>
+        <v>0.37249442001194005</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.31013136331583957</v>
+        <v>0.30672032764364598</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.30828123534083912</v>
+        <v>0.30489054863449466</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.26869230595600346</v>
+        <v>0.26573704522177555</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14480,43 +14480,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.2725605642972026</v>
+        <v>-0.26956275782670985</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16524394693295466</v>
+        <v>0.16342648161253059</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15933299493614786</v>
+        <v>0.15758054228616822</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17259979830675867</v>
+        <v>0.17070142832978158</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7207438035148695E-2</v>
+        <v>1.7018178927854937E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12005800277958709</v>
+        <v>0.11873752320656039</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15445882391958096</v>
+        <v>0.15275998071764979</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5105624141046721E-2</v>
+        <v>8.4169574601439964E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.798164790742421E-2</v>
+        <v>9.6903979100699353E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6954535458230033E-2</v>
+        <v>6.6218123937571982E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="I3" s="262">
         <f>-Market_Price</f>
-        <v>-22.48</v>
+        <v>-22.73</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>22.48</v>
+        <v>22.73</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="C86" s="264">
         <f>Market_Price</f>
-        <v>22.48</v>
+        <v>22.73</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11672702458118978</v>
+        <v>0.11252225662960313</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.2504074074074074</v>
+        <v>1.2171179290462264</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>16.961777399579361</v>
+        <v>16.244831286867644</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>18.21218480698677</v>
+        <v>17.461949215913869</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.37863476497451642</v>
+        <v>0.40423138170732364</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F5E823-607C-4AE4-93A1-5F4DFB35C8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2F61D2-678E-4BD2-9AA2-1FCA8E409D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3111,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3745,7 +3745,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3809,9 +3808,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3830,29 +3826,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4160,7 +4166,7 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4194,7 +4200,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>445</v>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       <c r="D22" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>442</v>
       </c>
     </row>
@@ -4378,7 +4384,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4388,14 +4394,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>29.309951346473134</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.11252225662960313</v>
       </c>
@@ -4408,18 +4414,18 @@
       <c r="B28" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>SIRI (USD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4427,18 +4433,18 @@
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>11.624652823058726</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>427</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4446,18 +4452,18 @@
       <c r="B30" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>17.461949215913869</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4465,18 +4471,18 @@
       <c r="B31" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>24.796949133193245</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>439</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4484,18 +4490,18 @@
       <c r="B32" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>22.440333461900007</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4523,13 +4529,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4636,7 +4642,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4644,14 +4650,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-496</v>
       </c>
@@ -4659,8 +4665,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4719,10 +4725,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4823,13 +4829,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4867,7 +4873,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4979,28 +4985,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>1.4851905363915479</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>0.95241105291674188</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>4.0148803043206254</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5275,13 +5281,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,13 +5300,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5364,7 +5370,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5397,7 +5403,7 @@
         <f>Scenarios!C83</f>
         <v>11.624652823058726</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5406,11 +5412,11 @@
       <c r="B145" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5433,7 +5439,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5466,7 +5472,7 @@
         <f>Scenarios!C93</f>
         <v>17.461949215913869</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5475,11 +5481,11 @@
       <c r="B153" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5535,7 +5541,7 @@
         <f>Scenarios!C99</f>
         <v>24.796949133193245</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5544,11 +5550,11 @@
       <c r="B161" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5604,7 +5610,7 @@
         <f>Scenarios!C105</f>
         <v>22.440333461900007</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5613,11 +5619,11 @@
       <c r="B169" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5656,13 +5662,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5699,22 +5705,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,6 +5744,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5754,17 +5771,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8125,11 +8131,11 @@
         <f t="shared" si="40"/>
         <v>670</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8159,11 +8165,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9386,7 +9392,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
@@ -11457,104 +11463,104 @@
         <v>0</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324">
+      <c r="P48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320">
+      <c r="P49" s="319">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13918,47 +13924,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>-0.83903614457831321</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4705882352941178</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.6290189612530914</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.5205479452054795</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>15.404580152671755</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.2067833698030634</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.5991403979783874</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.8639698846132475</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>2.3048142393485742</v>
       </c>
-      <c r="P113" s="329">
+      <c r="P113" s="328">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>2.4406365013222842</v>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13970,47 +13976,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.6120370370370369</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>2.030735455543359</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.57964212378996771</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>0.54367346938775507</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.59704142011834316</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>0.54602057390362746</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.65580755908279886</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.78592484792628292</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.73254376654547337</v>
       </c>
-      <c r="P114" s="329">
+      <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.60817403232674216</v>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15304,10 +15310,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15322,8 +15328,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15338,8 +15344,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15354,8 +15360,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16849,11 +16855,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16874,8 +16880,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16896,8 +16902,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16907,8 +16913,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -16921,8 +16927,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -16940,8 +16946,8 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -16958,8 +16964,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -16976,8 +16982,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17003,21 +17009,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17031,8 +17037,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17046,8 +17052,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17067,8 +17073,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17078,8 +17084,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17093,8 +17099,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17104,8 +17110,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17125,8 +17131,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17136,8 +17142,8 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17151,8 +17157,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17162,8 +17168,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17183,8 +17189,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17194,8 +17200,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17209,8 +17215,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17221,8 +17227,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17284,8 +17290,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17295,8 +17301,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17310,8 +17316,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17321,8 +17327,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17342,8 +17348,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17353,8 +17359,8 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17368,8 +17374,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17379,8 +17385,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17397,7 +17403,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17511,7 +17517,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>-1.0370265985797507</v>
       </c>
@@ -17604,7 +17610,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.60338887343606862</v>
       </c>
@@ -17693,7 +17699,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.40423138170732364</v>
       </c>
@@ -17703,7 +17709,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17714,7 +17720,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17726,7 +17732,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17738,7 +17744,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17754,7 +17760,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>0.15397508374994073</v>
       </c>
@@ -17810,7 +17816,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.23439581861974057</v>
       </c>
@@ -17819,32 +17825,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2F61D2-678E-4BD2-9AA2-1FCA8E409D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1BF3BB-B956-4C39-8678-44803C84284E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4909,7 +4909,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>56.987019341727418</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4963,7 +4963,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>10547</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5034,7 +5034,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>-372.31656312939253</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5065,7 +5065,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>625.79999999999995</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5100,7 +5100,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>26.591820192356398</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5159,111 +5159,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>5.5E-2</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>45.55 USD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>33.27 USD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>29.32 USD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>-0.01</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>24.88 USD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>-0.05</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>15.12 USD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-10547</v>
       </c>
       <c r="D86" s="248">
@@ -9512,7 +9512,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>-372.31656312939253</v>
       </c>
       <c r="D87" s="248">
@@ -9529,7 +9529,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>625.79999999999995</v>
       </c>
       <c r="D88" s="248">
@@ -15489,7 +15489,7 @@
         <v>1567.0163870892554</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15511,7 +15511,7 @@
         <v>1590.4586141311581</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15533,7 +15533,7 @@
         <v>1614.2515318315707</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15555,7 +15555,7 @@
         <v>1638.4003864470774</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15577,7 +15577,7 @@
         <v>1662.9105027171286</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15599,7 +15599,7 @@
         <v>1687.7872850381286</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15621,7 +15621,7 @@
         <v>1713.0362186550856</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15643,7 +15643,7 @@
         <v>1738.6628708710896</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15665,7 +15665,7 @@
         <v>1764.6728922748828</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15687,7 +15687,7 @@
         <v>1791.0720179867972</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>1.49597842339395E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15709,7 +15709,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15731,7 +15731,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15775,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15797,7 +15797,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15819,7 +15819,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15863,7 +15863,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15885,7 +15885,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -15907,7 +15907,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -15929,7 +15929,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -15951,7 +15951,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -15973,7 +15973,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -15995,7 +15995,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16017,7 +16017,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16039,7 +16039,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16061,7 +16061,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16083,7 +16083,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16127,7 +16127,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16828,7 +16828,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17045,7 +17045,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>26.591820192356398</v>
       </c>
       <c r="D22" t="str">
@@ -17092,7 +17092,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>29.318191600940459</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17150,7 +17150,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>24.878000087289131</v>
       </c>
       <c r="D33" t="str">
@@ -17208,7 +17208,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>33.269887669660939</v>
       </c>
       <c r="D39" t="str">
@@ -17309,7 +17309,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>15.121055640471935</v>
       </c>
       <c r="D51" t="str">
@@ -17367,7 +17367,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>45.548751974251395</v>
       </c>
       <c r="D57" t="str">
@@ -17455,7 +17455,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>29.310620301790603</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1BF3BB-B956-4C39-8678-44803C84284E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16028BC9-AA03-40F9-95CE-7DDBEEFA527F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16028BC9-AA03-40F9-95CE-7DDBEEFA527F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54748BED-084B-4B06-909B-B4EAB1F33FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2407,28 +2402,58 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Sirius XM</t>
+  </si>
+  <si>
+    <t>SIRI</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>TMT_05</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Sirius XM</t>
-  </si>
-  <si>
-    <t>SIRI</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>TMT_05</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2444,7 +2469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2463,6 +2488,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3111,7 +3137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3617,9 +3643,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3836,29 +3859,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3877,7 +3907,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3924,8 +3968,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4166,15 +4210,15 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>444</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4189,7 +4233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4198,10 +4242,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>445</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,9 +4259,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4238,20 +4282,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4267,17 +4311,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4291,7 +4335,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4318,73 +4362,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>449</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>442</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>444</v>
+        <v>435</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>444</v>
+        <v>436</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4394,14 +4442,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>29.309951346473134</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.11252225662960313</v>
       </c>
@@ -4412,96 +4460,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>434</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>SIRI (USD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>430</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C29" s="345">
+        <v>426</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>11.624652823058726</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>427</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>425</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C30" s="346">
+        <v>427</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>17.461949215913869</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C31" s="346">
+        <v>428</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>24.796949133193245</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>437</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C32" s="346">
+        <v>429</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>22.440333461900007</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4510,8 +4558,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4520,22 +4568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4547,13 +4595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4573,13 +4621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4608,13 +4656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4630,19 +4678,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4650,14 +4698,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-496</v>
       </c>
@@ -4665,8 +4713,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4700,13 +4748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4722,13 +4770,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4744,22 +4792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4788,26 +4836,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.20057023965412205</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>2.6115266168059832E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.130205090311977</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4820,22 +4876,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4844,7 +4900,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4853,7 +4909,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4864,7 +4920,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4873,42 +4929,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>56.987019341727418</v>
       </c>
@@ -4918,8 +4974,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4931,13 +4987,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4950,13 +5006,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4973,9 +5029,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>31.143697439289426</v>
       </c>
@@ -4985,28 +5041,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>1.4851905363915479</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>0.95241105291674188</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>4.0148803043206254</v>
       </c>
@@ -5044,9 +5100,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>-1.0993945571003985</v>
       </c>
@@ -5075,9 +5131,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.8478928470188039</v>
       </c>
@@ -5087,20 +5143,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>450</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>26.591820192356398</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5109,10 +5165,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>-38.360607814419353</v>
       </c>
@@ -5122,8 +5178,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5132,49 +5188,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>5.5E-2</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>45.55 USD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5192,11 +5248,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>33.27 USD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.22499999999999998</v>
       </c>
@@ -5214,11 +5270,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>29.32 USD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
@@ -5236,11 +5292,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>24.88 USD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.22499999999999998</v>
       </c>
@@ -5258,11 +5314,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>15.12 USD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5300,22 +5356,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5326,7 +5382,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5335,7 +5391,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5355,22 +5411,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>SIRI</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5403,20 +5459,20 @@
         <f>Scenarios!C83</f>
         <v>11.624652823058726</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5432,14 +5488,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5472,20 +5528,20 @@
         <f>Scenarios!C93</f>
         <v>17.461949215913869</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5501,12 +5557,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5535,26 +5591,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>24.796949133193245</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5570,12 +5626,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5604,26 +5660,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>22.440333461900007</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5638,8 +5694,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5648,113 +5704,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5771,6 +5816,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5783,7 +5839,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6283,7 +6339,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>1741</v>
@@ -6319,7 +6375,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-970</v>
@@ -6355,7 +6411,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-916</v>
@@ -6414,7 +6470,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7683,7 +7739,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8131,11 +8187,11 @@
         <f t="shared" si="40"/>
         <v>670</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8165,11 +8221,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8272,17 +8328,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8366,7 +8422,7 @@
       <c r="C4" s="19">
         <v>676</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8376,7 +8432,7 @@
       <c r="G4" s="19">
         <v>162</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8387,7 +8443,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8397,7 +8453,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8408,7 +8464,7 @@
       <c r="C6" s="19">
         <v>0</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8418,7 +8474,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8429,7 +8485,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8439,7 +8495,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8450,7 +8506,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8460,7 +8516,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8471,7 +8527,7 @@
       <c r="C9" s="19">
         <v>290</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8481,7 +8537,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8492,10 +8548,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8504,10 +8560,10 @@
       <c r="C11" s="19">
         <v>21</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8565,7 +8621,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8574,7 +8630,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8585,7 +8641,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8594,7 +8650,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8605,7 +8661,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8614,7 +8670,7 @@
       <c r="G17" s="19">
         <v>1043</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8625,7 +8681,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8634,7 +8690,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8645,7 +8701,7 @@
       <c r="C19" s="19">
         <v>2109</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8654,7 +8710,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8665,7 +8721,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8674,7 +8730,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8686,7 +8742,7 @@
         <f>8610+1579</f>
         <v>10189</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.2</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8695,7 +8751,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8706,10 +8762,10 @@
       <c r="C22" s="19">
         <v>0</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8719,10 +8775,10 @@
         <f>12390+641</f>
         <v>13031</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9055,13 +9111,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9077,7 +9133,7 @@
         <f>H29</f>
         <v>-12991.05</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9092,23 +9148,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-38.360607814419353</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9122,7 +9178,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>5.4478305785123968</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9133,22 +9189,22 @@
         <f>G29/G32</f>
         <v>0.40238363431561353</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9162,7 +9218,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>7.3567411460708318E-2</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9176,22 +9232,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9213,22 +9269,22 @@
         <f>G39/G32</f>
         <v>7.6632389811416735E-2</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9242,7 +9298,7 @@
         <f>G28/G29</f>
         <v>0</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9261,13 +9317,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9295,7 +9351,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9305,7 +9361,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9315,7 +9371,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9325,26 +9381,26 @@
         <f>SUM(C66:C69)</f>
         <v>162</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9355,65 +9411,65 @@
         <v>-534.31656312939253</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>0.27914886356305812</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>0.30319105036010147</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>534.31656312939253</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9427,7 +9483,7 @@
         <f>G7*H7+G17*H17</f>
         <v>625.79999999999995</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9441,7 +9497,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9455,7 +9511,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9469,11 +9525,11 @@
         <f>SUM(D79:D81)</f>
         <v>625.79999999999995</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9484,76 +9540,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-10547</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-31.143697439289426</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>-372.31656312939253</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>-1.0993945571003985</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>625.79999999999995</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.8478928470188039</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-10293.516563129393</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>-30.395199149371017</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
@@ -9674,7 +9730,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9688,7 +9744,7 @@
         <v>8837.75</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9744,7 +9800,7 @@
         <f>C25</f>
         <v>-4748.2725559527107</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5392</v>
@@ -9799,7 +9855,7 @@
         <f>C4+C5</f>
         <v>4089.4774440472893</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>3307</v>
@@ -9854,7 +9910,7 @@
         <f>C35</f>
         <v>-1462.5</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1371</v>
@@ -9910,7 +9966,7 @@
         <v>2626.9774440472893</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9966,7 +10022,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>578</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>578</v>
@@ -10021,7 +10077,7 @@
         <f>-C4*C78</f>
         <v>-632.31340126010366</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-728</v>
@@ -10077,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10133,7 +10189,7 @@
         <f>C50</f>
         <v>-496</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-496</v>
@@ -10188,7 +10244,7 @@
         <f>SUM(C8:C12)</f>
         <v>2076.6640427871857</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1290</v>
@@ -10243,7 +10299,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-532.74436101182232</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-210</v>
@@ -10299,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10356,7 +10412,7 @@
         <v>1543.9196817753634</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10413,8 +10469,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10438,8 +10494,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10464,7 +10520,7 @@
         <v>1543.9196817753634</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10560,7 +10616,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10584,7 +10640,7 @@
         <v>-4109.1377805440734</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10641,7 +10697,7 @@
         <v>-639.13477540863767</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10698,7 +10754,7 @@
         <v>-4748.2725559527107</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10747,14 +10803,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10766,8 +10822,8 @@
         <v>0.46495293265187104</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10826,8 +10882,8 @@
         <v>7.2318720874502862E-2</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10884,7 +10940,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.53727165352637385</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.61984136107598575</v>
@@ -10932,14 +10988,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10950,8 +11006,8 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-1462.5</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11008,8 +11064,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11067,7 +11123,7 @@
         <v>-1462.5</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11116,14 +11172,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11136,7 +11192,7 @@
         <v>0.16548329608780515</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11194,7 +11250,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11250,7 +11306,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.16548329608780515</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.15760432233590069</v>
@@ -11298,26 +11354,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11396,7 +11452,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11407,7 +11463,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-496</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-496</v>
@@ -11456,111 +11512,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323">
+      <c r="P48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319">
+      <c r="P49" s="318">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11574,7 +11630,7 @@
         <f>C47+C48</f>
         <v>-496</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-496</v>
@@ -11622,14 +11678,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11643,8 +11699,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11670,8 +11726,8 @@
         <f>G54</f>
         <v>4.7027590784109223E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11697,7 +11753,7 @@
         <f>-C8/C47</f>
         <v>5.2963254920308254</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>3.903225806451613</v>
@@ -11745,14 +11801,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11766,7 +11822,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11821,7 +11877,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11876,7 +11932,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11931,7 +11987,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11982,11 +12038,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12042,7 +12098,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-3305</v>
@@ -12090,14 +12146,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12111,7 +12167,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12136,7 +12192,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12161,7 +12217,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12187,7 +12243,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12215,7 +12271,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12237,7 +12293,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12261,7 +12317,7 @@
         <v>0.53727165352637385</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12318,7 +12374,7 @@
         <v>0.46272834647362615</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12375,7 +12431,7 @@
         <v>0.16548329608780515</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12432,7 +12488,7 @@
         <v>0.297245050385821</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12489,7 +12545,7 @@
         <v>6.5401261633334276E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12546,8 +12602,8 @@
         <v>7.1546875761376333E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>452</v>
+      <c r="E78" s="295" t="s">
+        <v>460</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12605,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12662,7 +12718,7 @@
         <v>5.6122881955248789E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12719,7 +12775,7 @@
         <v>0.23497655430253014</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12776,7 +12832,7 @@
         <v>6.0280542107643047E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12829,12 +12885,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12891,7 +12947,7 @@
         <v>0.17469601219488709</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12943,26 +12999,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12972,7 +13028,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12998,7 +13054,7 @@
         <v>0.17469601219488709</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13047,14 +13103,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13066,7 +13122,7 @@
         <f>G90</f>
         <v>0.59360000000000002</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.59360000000000002</v>
@@ -13122,7 +13178,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>201.02620160000001</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>201.02620160000001</v>
@@ -13177,7 +13233,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.130205090311977</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.18613537185185186</v>
@@ -13226,13 +13282,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>2.6115266168059832E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>2.6115266168059832E-2</v>
@@ -13280,7 +13336,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13289,7 +13345,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13313,7 +13369,7 @@
         <v>1.5950109207955032E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13370,7 +13426,7 @@
         <v>0.60981708743192686</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13448,7 +13504,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13463,7 +13519,7 @@
         <v>27521</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13520,7 +13576,7 @@
         <v>676</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13577,7 +13633,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13634,7 +13690,7 @@
         <v>16447</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13691,7 +13747,7 @@
         <v>11074</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13740,7 +13796,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13749,7 +13805,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13775,7 +13831,7 @@
         <v>7.649005685836327E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13832,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13889,7 +13945,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13908,63 +13964,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>-0.83903614457831321</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4705882352941178</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.6290189612530914</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.5205479452054795</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>15.404580152671755</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.2067833698030634</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.5991403979783874</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.8639698846132475</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>2.3048142393485742</v>
       </c>
-      <c r="P113" s="328">
+      <c r="P113" s="327">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>2.4406365013222842</v>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13972,58 +14028,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.6120370370370369</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>2.030735455543359</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.57964212378996771</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>0.54367346938775507</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.59704142011834316</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>0.54602057390362746</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.65580755908279886</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.78592484792628292</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.73254376654547337</v>
       </c>
-      <c r="P114" s="328">
+      <c r="P114" s="327">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.60817403232674216</v>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14032,7 +14088,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14088,7 +14144,7 @@
         <f>C81</f>
         <v>0.23497655430253014</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.14829290723071617</v>
@@ -14142,7 +14198,7 @@
         <f>C4/C101</f>
         <v>0.32112750263435197</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.31608589804149556</v>
@@ -14197,7 +14253,7 @@
         <v>2.4851905363915479</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14254,7 +14310,7 @@
         <v>0.23722028571855602</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14350,7 +14406,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14375,7 +14431,7 @@
         <v>4.5589615473381944</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14432,7 +14488,7 @@
         <v>0.20057023965412205</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14481,7 +14537,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15214,7 +15270,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15282,7 +15338,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15292,7 +15348,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15310,10 +15366,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15328,8 +15384,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15344,8 +15400,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15360,8 +15416,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16706,7 +16762,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16737,12 +16793,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16757,6 +16813,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>201.02620160000001</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>2512.8275199999998</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>7.42</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>7.7740016137890926</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>446</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>204.03351020130444</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>188.91991685305965</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>207.08580749040925</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>177.54270189506965</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>210.1837664883769</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>166.85065037752827</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>213.32807028451975</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>156.80250009858199</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>216.51941218701884</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>147.35947376611023</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>219.75849587579603</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>138.48512935044263</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>223.04603555767304</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>130.14521944919861</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>226.38275612385146</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>122.30755912151605</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>229.76939330974881</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>114.94190168162382</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>233.20669385722584</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>1.49597842339395E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>108.01982197242555</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>2550.4188775163052</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>1181.3374159538025</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>2632.7122905193592</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>2632.7122905193592</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>-0.05</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>-0.01</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>5.5E-2</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>2320.0884246775549</v>
+      </c>
+      <c r="C51" s="124">
+        <v>2473.167207375589</v>
+      </c>
+      <c r="D51" s="124">
+        <v>2573.4116924002578</v>
+      </c>
+      <c r="E51" s="124">
+        <v>2656.2999649722678</v>
+      </c>
+      <c r="F51" s="124">
+        <v>2741.696068748121</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>2167.3569542617097</v>
+      </c>
+      <c r="C52" s="124">
+        <v>2437.2570765185151</v>
+      </c>
+      <c r="D52" s="124">
+        <v>2633.0461449494678</v>
+      </c>
+      <c r="E52" s="124">
+        <v>2807.2951361558858</v>
+      </c>
+      <c r="F52" s="124">
+        <v>2999.2436793458351</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>2007.0271960951834</v>
+      </c>
+      <c r="C53" s="124">
+        <v>2395.9764601375809</v>
+      </c>
+      <c r="D53" s="124">
+        <v>2705.932441682487</v>
+      </c>
+      <c r="E53" s="124">
+        <v>3001.5671768381071</v>
+      </c>
+      <c r="F53" s="124">
+        <v>3348.7284045621163</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>1868.2167608434065</v>
+      </c>
+      <c r="C54" s="124">
+        <v>2356.9817414063832</v>
+      </c>
+      <c r="D54" s="124">
+        <v>2779.2194557307012</v>
+      </c>
+      <c r="E54" s="124">
+        <v>3207.7525551693534</v>
+      </c>
+      <c r="F54" s="124">
+        <v>3741.533780102443</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>1758.107875125437</v>
+      </c>
+      <c r="C55" s="124">
+        <v>2323.387920872176</v>
+      </c>
+      <c r="D55" s="124">
+        <v>2846.4604396038576</v>
+      </c>
+      <c r="E55" s="124">
+        <v>3407.8678901723379</v>
+      </c>
+      <c r="F55" s="124">
+        <v>4146.699500803451</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>1674.9349111022073</v>
+      </c>
+      <c r="C56" s="124">
+        <v>2295.9585520816736</v>
+      </c>
+      <c r="D56" s="124">
+        <v>2904.9538058065068</v>
+      </c>
+      <c r="E56" s="124">
+        <v>3592.3916549285623</v>
+      </c>
+      <c r="F56" s="124">
+        <v>4545.0466757254017</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>-0.05</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>-0.01</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>5.5E-2</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>7.42</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>7.42</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>7.42</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>7.42</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>7.42</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>6.850870572727354</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>7.3028890891512006</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>7.5988959073521745</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>7.843652452554414</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>8.0958142443899437</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>6.399877616996922</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>7.1968518984412357</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>7.7749874354786801</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>8.2895183789919145</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>8.8563134252629077</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>5.9264480655744576</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>7.0749564754133427</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>7.9902096572406425</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>8.8631743622971602</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>9.888289014699625</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>5.516561823335203</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>6.9598109627657072</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>8.2066151366894466</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>9.4720086316774346</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>11.048183939166716</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>5.1914269203127565</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>6.8606134864646604</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>8.4051676025343056</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>10.062918980240532</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>12.244577095351776</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>4.9458297242694869</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>6.7796187047672962</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>8.5778896750877198</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>10.607789777616704</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>13.420836116074724</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>5.5E-2</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>9.888289014699625</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>8.2895183789919145</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>7.7749874354786801</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>-0.01</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>7.1968518984412357</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>-0.05</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>5.9264480655744576</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16777,19 +18284,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-22.73</v>
       </c>
@@ -16806,19 +18313,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.59360000000000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>0.59360000000000002</v>
       </c>
@@ -16832,13 +18339,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>29.903551346473133</v>
       </c>
@@ -16855,15 +18362,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16880,12 +18387,12 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16902,37 +18409,37 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>448</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16946,12 +18453,12 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16964,12 +18471,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16982,8 +18489,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16999,7 +18506,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17009,25 +18516,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17037,23 +18544,23 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>26.591820192356398</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17073,8 +18580,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17084,23 +18591,23 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>29.318191600940459</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17110,8 +18617,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17131,8 +18638,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17142,23 +18649,23 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>24.878000087289131</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17168,8 +18675,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17189,8 +18696,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17200,23 +18707,23 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>33.269887669660939</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17227,8 +18734,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17290,8 +18797,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17301,23 +18808,23 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>15.121055640471935</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17327,12 +18834,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17348,8 +18855,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17359,23 +18866,23 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>45.548751974251395</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17385,8 +18892,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17401,16 +18908,16 @@
         <v>USD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17419,10 +18926,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17434,8 +18941,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17446,8 +18953,8 @@
         <v>1.49597842339395E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17455,30 +18962,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>29.310620301790603</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17486,38 +18993,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>-1.0370265985797507</v>
       </c>
@@ -17537,10 +19044,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17561,12 +19068,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17610,7 +19117,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.60338887343606862</v>
       </c>
@@ -17620,14 +19127,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>22.73</v>
       </c>
@@ -17638,9 +19145,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.11252225662960313</v>
       </c>
@@ -17650,12 +19157,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17699,28 +19206,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.40423138170732364</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17732,7 +19239,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17744,23 +19251,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>24.796949133193245</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>0.15397508374994073</v>
       </c>
@@ -17770,12 +19277,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17804,19 +19311,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>22.440333461900007</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.23439581861974057</v>
       </c>
@@ -17825,33 +19332,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292A585F-2265-E148-824E-21FED52C560C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588FFAF9-6E72-384B-819E-E4936C6C9FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1220" yWindow="6780" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3874,6 +3874,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3909,9 +3912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4220,7 +4220,7 @@
       <c r="C1" s="44">
         <v>45754</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>461</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4375,13 +4375,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4581,22 +4581,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4608,13 +4608,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4634,13 +4634,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4669,13 +4669,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4691,13 +4691,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4783,13 +4783,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4805,22 +4805,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4889,22 +4889,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4948,22 +4948,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -5000,13 +5000,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5019,13 +5019,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5156,13 +5156,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5201,13 +5201,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5350,13 +5350,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5369,22 +5369,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5717,13 +5717,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5731,13 +5731,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5760,13 +5760,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15379,10 +15379,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15397,8 +15397,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15413,8 +15413,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15429,8 +15429,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -16909,8 +16909,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18375,11 +18375,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18400,8 +18400,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18422,8 +18422,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18433,8 +18433,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18447,8 +18447,8 @@
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18466,8 +18466,8 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18484,8 +18484,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18502,8 +18502,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18529,21 +18529,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18557,8 +18557,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18572,8 +18572,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18593,8 +18593,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18604,8 +18604,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18619,8 +18619,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18630,8 +18630,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18651,8 +18651,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18662,8 +18662,8 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18677,8 +18677,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18688,8 +18688,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18709,8 +18709,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18720,8 +18720,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18735,8 +18735,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18747,8 +18747,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18810,8 +18810,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18821,8 +18821,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18836,8 +18836,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18847,8 +18847,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18868,8 +18868,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18879,8 +18879,8 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18894,8 +18894,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -18905,8 +18905,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588FFAF9-6E72-384B-819E-E4936C6C9FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE014AD-B815-4A17-A03A-CE688C9B9E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="6780" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2491,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3915,7 +3904,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4204,7 +4193,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4213,7 +4202,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4230,7 +4219,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4244,7 +4233,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>416</v>
       </c>
@@ -4253,7 +4242,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4261,7 +4250,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4270,7 +4259,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4280,7 +4269,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4290,17 +4279,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>418</v>
       </c>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4322,7 +4311,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>417</v>
       </c>
@@ -4332,7 +4321,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>421</v>
       </c>
@@ -4346,7 +4335,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>420</v>
       </c>
@@ -4360,7 +4349,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4370,11 +4359,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4383,14 +4372,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4405,7 +4394,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4418,7 +4407,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>435</v>
       </c>
@@ -4426,7 +4415,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>436</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4450,28 +4439,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>29.309951346473134</v>
+        <v>33.230161875234657</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11252225662960313</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.15812491412146712</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>434</v>
       </c>
@@ -4490,13 +4479,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>11.624652823058726</v>
+        <v>13.980827278242025</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,16 +4495,16 @@
         <v>425</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>17.461949215913869</v>
+        <v>19.634697914672664</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4528,13 +4517,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>24.796949133193245</v>
+        <v>28.292642107173183</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4544,16 +4533,16 @@
         <v>437</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>22.440333461900007</v>
+        <v>25.250185101195886</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4566,11 +4555,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4580,7 +4569,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4589,7 +4578,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4598,7 +4587,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4607,7 +4596,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4616,7 +4605,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4629,11 +4618,11 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4642,7 +4631,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4655,7 +4644,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4668,7 +4657,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4677,7 +4666,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4690,7 +4679,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4699,7 +4688,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4714,7 +4703,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4729,7 +4718,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4742,12 +4731,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4760,7 +4749,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4769,7 +4758,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4782,7 +4771,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4791,7 +4780,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4804,7 +4793,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4813,7 +4802,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4822,7 +4811,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4835,7 +4824,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4848,7 +4837,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4858,7 +4847,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4874,7 +4863,7 @@
         <v>0.130205090311977</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4884,10 +4873,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4897,7 +4886,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4906,21 +4895,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>431</v>
       </c>
@@ -4929,25 +4918,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4956,7 +4945,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4965,7 +4954,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4973,20 +4962,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>56.987019341727418</v>
+        <v>60.786153964509253</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4996,10 +4985,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5008,17 +4997,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5027,7 +5016,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5040,7 +5029,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5053,7 +5042,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5062,7 +5051,7 @@
         <v>1.4851905363915479</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5071,7 +5060,7 @@
         <v>0.95241105291674188</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5080,12 +5069,12 @@
         <v>4.0148803043206254</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5098,7 +5087,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5111,7 +5100,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5124,12 +5113,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5142,7 +5131,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5155,7 +5144,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5164,20 +5153,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>450</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5190,7 +5179,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5200,7 +5189,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5209,7 +5198,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5226,7 +5215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5241,14 +5230,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>45.55 USD</v>
+        <v>50.32 USD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5263,14 +5252,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.27 USD</v>
+        <v>37.36 USD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5285,14 +5274,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>29.32 USD</v>
+        <v>33.24 USD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5307,14 +5296,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>24.88 USD</v>
+        <v>28.6 USD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5329,27 +5318,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>15.12 USD</v>
+        <v>18.34 USD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>29.309951346473134</v>
+        <v>33.230161875234657</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5358,7 +5347,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5368,7 +5357,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5377,7 +5366,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5386,12 +5375,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5400,16 +5389,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5422,7 +5411,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5435,49 +5424,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>0.94318367346938758</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.98374913197498015</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>10.681469149589338</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>12.997078146267045</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>11.624652823058726</v>
+        <v>13.980827278242025</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>417</v>
       </c>
@@ -5490,21 +5479,21 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.60338887343606862</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.57927297102150221</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5513,7 +5502,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5523,30 +5512,30 @@
         <v>1.2171179290462264</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>16.244831286867644</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>18.417579985626439</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>17.461949215913869</v>
+        <v>19.634697914672664</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>417</v>
       </c>
@@ -5559,63 +5548,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.40423138170732364</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.40913023570596097</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>1.5297647716303417</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>1.5436720791879954</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>23.267184361562904</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>26.748970027985187</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>24.796949133193245</v>
+        <v>28.292642107173183</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>417</v>
       </c>
@@ -5628,21 +5617,21 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.15397508374994073</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.14858548648061942</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>424</v>
       </c>
@@ -5651,7 +5640,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5661,30 +5650,30 @@
         <v>1.4321212155571821</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>21.008212246342826</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>23.818063885638704</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>22.440333461900007</v>
+        <v>25.250185101195886</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>417</v>
       </c>
@@ -5697,16 +5686,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.23439581861974057</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.24009625632933929</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5716,7 +5705,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5725,12 +5714,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5739,27 +5728,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5768,12 +5757,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5782,7 +5771,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5791,22 +5780,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5867,15 +5856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>USD</v>
@@ -5924,7 +5913,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5940,7 +5929,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5948,7 +5937,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5984,7 +5973,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6020,7 +6009,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6042,7 +6031,7 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6064,7 +6053,7 @@
       <c r="L7" s="188"/>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6080,7 +6069,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6096,7 +6085,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6112,7 +6101,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6128,7 +6117,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6164,7 +6153,7 @@
       </c>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6180,7 +6169,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6216,7 +6205,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6252,7 +6241,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6272,13 +6261,13 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6298,7 +6287,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6324,7 +6313,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6350,7 +6339,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6386,7 +6375,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6422,7 +6411,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6458,7 +6447,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (USD)</v>
@@ -6478,7 +6467,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6486,7 +6475,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6523,7 +6512,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6542,7 +6531,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6579,7 +6568,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6616,7 +6605,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6635,7 +6624,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6651,12 +6640,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6705,7 +6694,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6754,7 +6743,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6803,7 +6792,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6852,7 +6841,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6901,7 +6890,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -6950,7 +6939,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -6999,7 +6988,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7048,7 +7037,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7097,7 +7086,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7146,7 +7135,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7195,7 +7184,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7244,7 +7233,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7293,12 +7282,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7347,7 +7336,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7396,12 +7385,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7450,7 +7439,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7499,7 +7488,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7548,7 +7537,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7597,13 +7586,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7652,7 +7641,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7701,7 +7690,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7750,7 +7739,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7799,7 +7788,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7848,12 +7837,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7903,7 +7892,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -7952,7 +7941,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8002,7 +7991,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8051,7 +8040,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8101,7 +8090,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8117,13 +8106,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8172,7 +8161,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8206,7 +8195,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8240,7 +8229,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8289,7 +8278,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8370,7 +8359,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8381,7 +8370,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8397,7 +8386,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8408,7 +8397,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8428,7 +8417,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8449,7 +8438,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8470,7 +8459,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8491,7 +8480,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8512,7 +8501,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8533,7 +8522,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8554,7 +8543,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8566,7 +8555,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8578,7 +8567,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8602,12 +8591,12 @@
         <v>145.80000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8627,7 +8616,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8647,7 +8636,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8667,7 +8656,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8687,7 +8676,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8707,7 +8696,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8727,7 +8716,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8747,7 +8736,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8768,7 +8757,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8780,7 +8769,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8793,7 +8782,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8817,7 +8806,7 @@
         <v>625.79999999999995</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8834,7 +8823,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8853,7 +8842,7 @@
         <v>-12991.05</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8868,7 +8857,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8887,7 +8876,7 @@
         <v>-12991.05</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8903,7 +8892,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8920,7 +8909,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8940,7 +8929,7 @@
         <v>3455.9500000000003</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8951,7 +8940,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -8964,7 +8953,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -8983,7 +8972,7 @@
         <v>2684.3500000000004</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8999,7 +8988,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9015,7 +9004,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9031,7 +9020,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9050,7 +9039,7 @@
         <v>210.9</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9070,7 +9059,7 @@
         <v>771.59999999999991</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9090,7 +9079,7 @@
         <v>145.79999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9109,7 +9098,7 @@
         <v>625.79999999999995</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9120,7 +9109,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9134,7 +9123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9148,7 +9137,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (USD)</v>
@@ -9163,10 +9152,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9179,7 +9168,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9193,7 +9182,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9204,10 +9193,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9219,7 +9208,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9233,7 +9222,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9247,10 +9236,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9262,7 +9251,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9273,7 +9262,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9284,10 +9273,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9299,7 +9288,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9315,7 +9304,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9326,7 +9315,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9340,7 +9329,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9356,7 +9345,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9366,7 +9355,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9376,7 +9365,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9386,7 +9375,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9396,10 +9385,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9411,7 +9400,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9427,7 +9416,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9443,7 +9432,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9456,7 +9445,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9469,10 +9458,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9484,7 +9473,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9498,7 +9487,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9512,7 +9501,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9526,7 +9515,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9540,7 +9529,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9551,7 +9540,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9559,7 +9548,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9576,7 +9565,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9593,7 +9582,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9610,7 +9599,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9641,19 +9630,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9710,7 +9699,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9733,7 +9722,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9747,7 +9736,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9804,7 +9793,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9859,7 +9848,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9914,7 +9903,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -9969,7 +9958,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10026,7 +10015,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10081,7 +10070,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10136,7 +10125,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10193,7 +10182,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10248,7 +10237,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10303,7 +10292,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10358,7 +10347,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10415,7 +10404,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10472,7 +10461,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10498,7 +10487,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10523,7 +10512,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10580,7 +10569,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10599,7 +10588,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10622,7 +10611,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10643,7 +10632,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10700,7 +10689,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10757,7 +10746,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10814,18 +10803,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10884,7 +10873,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10944,7 +10933,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -10999,18 +10988,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11067,7 +11056,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11126,7 +11115,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11183,18 +11172,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11252,7 +11241,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11310,7 +11299,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11365,18 +11354,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11434,10 +11423,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11460,14 +11449,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11522,7 +11511,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11577,7 +11566,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11634,7 +11623,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11689,11 +11678,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11703,7 +11692,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11730,7 +11719,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11757,7 +11746,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11812,11 +11801,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11826,7 +11815,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11881,7 +11870,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11936,7 +11925,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -11991,7 +11980,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12046,7 +12035,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12102,7 +12091,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12157,11 +12146,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12171,7 +12160,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12196,7 +12185,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12221,7 +12210,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12246,7 +12235,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12273,10 +12262,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12299,7 +12288,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12320,7 +12309,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12377,7 +12366,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12434,7 +12423,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12491,7 +12480,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12548,7 +12537,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12605,7 +12594,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12664,7 +12653,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12721,7 +12710,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12778,7 +12767,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12835,7 +12824,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12892,7 +12881,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12950,7 +12939,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13007,7 +12996,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13033,7 +13022,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13057,7 +13046,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13114,18 +13103,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13181,7 +13170,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13237,7 +13226,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13292,7 +13281,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13347,11 +13336,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13372,7 +13361,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13429,7 +13418,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13486,10 +13475,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13512,7 +13501,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13522,7 +13511,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13579,7 +13568,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13636,7 +13625,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13693,7 +13682,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13750,7 +13739,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13807,11 +13796,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13834,7 +13823,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13891,7 +13880,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -13948,7 +13937,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -13975,18 +13964,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14038,7 +14027,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14090,11 +14079,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14148,7 +14137,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14203,7 +14192,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14257,7 +14246,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14313,7 +14302,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14370,7 +14359,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14389,7 +14378,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14412,7 +14401,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14433,7 +14422,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14491,7 +14480,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14548,7 +14537,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14598,688 +14587,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15301,16 +15290,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15322,7 +15311,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15335,7 +15324,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15356,24 +15345,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>19298.996022192041</v>
+        <v>20585.595757004845</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15385,7 +15374,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15401,7 +15390,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15417,7 +15406,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15433,13 +15422,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>9005.4794590626479</v>
+        <v>10292.079193875452</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15447,7 +15436,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15461,13 +15450,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15475,10 +15464,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15488,13 +15477,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15504,7 +15493,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15514,13 +15503,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.310620301790603</v>
+        <v>33.228136210024012</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15528,10 +15517,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15549,7 +15538,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15563,15 +15552,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>1450.9410991567179</v>
+        <v>1457.6896624086096</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15585,15 +15574,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>1363.561911978016</v>
+        <v>1376.2757071984063</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15607,15 +15596,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>1281.4449110840974</v>
+        <v>1299.4088323948902</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15629,15 +15618,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>1204.2731948718474</v>
+        <v>1226.8350773573889</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15651,15 +15640,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>1131.7489463202289</v>
+        <v>1158.3146654932873</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15673,15 +15662,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>1063.5922836705254</v>
+        <v>1093.6212120596044</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15695,15 +15684,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>999.54018032140709</v>
+        <v>1032.5409762099307</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15717,15 +15706,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>939.34544977052622</v>
+        <v>974.87215481556518</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15739,15 +15728,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>882.77579168539467</v>
+        <v>920.42421572770388</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15761,15 +15750,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>829.61289542217889</v>
+        <v>869.01726827784523</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15791,7 +15780,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15813,7 +15802,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15835,7 +15824,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15857,7 +15846,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15879,7 +15868,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15901,7 +15890,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15923,7 +15912,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15945,7 +15934,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15967,7 +15956,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15989,7 +15978,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16011,7 +16000,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16033,7 +16022,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16055,7 +16044,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16077,7 +16066,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16099,7 +16088,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16121,7 +16110,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16143,7 +16132,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16165,7 +16154,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16187,7 +16176,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16209,13 +16198,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>19587.704838615693</v>
+        <v>20893.55182785674</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16223,30 +16212,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>9072.8973277716505</v>
+        <v>10137.424487528053</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>20219.733992052592</v>
+        <v>21546.424259471285</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16256,10 +16245,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>20219.733992052592</v>
+        <v>21546.424259471285</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16283,141 +16272,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>17818.722901835274</v>
+        <v>19031.587888731501</v>
       </c>
       <c r="C56" s="124">
-        <v>18994.397234776105</v>
+        <v>20266.082975871774</v>
       </c>
       <c r="D56" s="124">
-        <v>19764.294055126818</v>
+        <v>21073.429731022359</v>
       </c>
       <c r="E56" s="124">
-        <v>20400.891843841579</v>
+        <v>21740.394521675335</v>
       </c>
       <c r="F56" s="124">
-        <v>21056.750255914718</v>
+        <v>22427.000625887511</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>16645.715993657614</v>
+        <v>17813.688084504152</v>
       </c>
       <c r="C57" s="124">
-        <v>18718.600560690382</v>
+        <v>19979.681198943603</v>
       </c>
       <c r="D57" s="124">
-        <v>20222.298057937485</v>
+        <v>21549.099355808394</v>
       </c>
       <c r="E57" s="124">
-        <v>21560.563641786088</v>
+        <v>22944.90854943305</v>
       </c>
       <c r="F57" s="124">
-        <v>23034.765170543775</v>
+        <v>24481.697611840682</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>15414.352782109056</v>
+        <v>16505.921872174516</v>
       </c>
       <c r="C58" s="124">
-        <v>18401.557530483009</v>
+        <v>19642.910127301682</v>
       </c>
       <c r="D58" s="124">
-        <v>20782.078758971373</v>
+        <v>22143.781608213849</v>
       </c>
       <c r="E58" s="124">
-        <v>23052.610075736844</v>
+        <v>24530.138787807649</v>
       </c>
       <c r="F58" s="124">
-        <v>25718.874711721473</v>
+        <v>27333.73532083226</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>14348.262086889838</v>
+        <v>15347.362003280659</v>
       </c>
       <c r="C59" s="124">
-        <v>18102.070631485709</v>
+        <v>19317.395287097537</v>
       </c>
       <c r="D59" s="124">
-        <v>21344.937045637544</v>
+        <v>22755.62861090753</v>
       </c>
       <c r="E59" s="124">
-        <v>24636.153221686189</v>
+        <v>26251.683643453507</v>
       </c>
       <c r="F59" s="124">
-        <v>28735.695134019465</v>
+        <v>30613.825499722654</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>13502.604782293343</v>
+        <v>14406.891789847168</v>
       </c>
       <c r="C60" s="124">
-        <v>17844.063663757221</v>
+        <v>19030.418556472443</v>
       </c>
       <c r="D60" s="124">
-        <v>21861.360664038679</v>
+        <v>23330.105243206235</v>
       </c>
       <c r="E60" s="124">
-        <v>26173.077273760493</v>
+        <v>27961.560939178646</v>
       </c>
       <c r="F60" s="124">
-        <v>31847.445371511814</v>
+        <v>34076.150355479913</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>12863.820508775741</v>
+        <v>13679.863491555012</v>
       </c>
       <c r="C61" s="124">
-        <v>17633.400864593372</v>
+        <v>18790.620516452815</v>
       </c>
       <c r="D61" s="124">
-        <v>22310.600905433981</v>
+        <v>23841.53694236459</v>
       </c>
       <c r="E61" s="124">
-        <v>27590.255083891392</v>
+        <v>29575.106189105543</v>
       </c>
       <c r="F61" s="124">
-        <v>34906.827873129027</v>
+        <v>37559.873600067469</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16427,7 +16416,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>-0.05</v>
@@ -16450,193 +16439,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>22.220797324440973</v>
+        <v>25.802204377309447</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>25.692385995366131</v>
+        <v>29.447481848077047</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>27.965774981094164</v>
+        <v>31.831454832907035</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>29.845552066734935</v>
+        <v>33.800901087079346</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>31.782202863038972</v>
+        <v>35.828345172558933</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>18.757085155816586</v>
+        <v>22.205930269579632</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>24.878000087289131</v>
+        <v>28.601780673645852</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>29.318191600940459</v>
+        <v>33.236035365323517</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>33.269887669660939</v>
+        <v>37.357649019369674</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>37.622982044949396</v>
+        <v>41.895554925090032</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>15.121055640471935</v>
+        <v>18.344294236762746</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>23.941819921553485</v>
+        <v>27.607346582290845</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>30.971139433058855</v>
+        <v>34.992042205318839</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>37.6756753537733</v>
+        <v>42.0385943986767</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>45.548751974251395</v>
+        <v>50.317191361448984</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>11.973050894596421</v>
+        <v>14.923241992320429</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>23.057480358701209</v>
+        <v>26.646150441652132</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>32.633174910552746</v>
+        <v>36.798733959469601</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>42.351639004053659</v>
+        <v>47.122056246823071</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>54.456966865757792</v>
+        <v>60.002802066383765</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>9.475952645646176</v>
+        <v>12.146175548987102</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>22.29562476562597</v>
+        <v>25.798751515824463</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>34.158095828537768</v>
+        <v>38.495076656184573</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>46.889943513863919</v>
+        <v>52.171065553391209</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>63.645495158457024</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>70.226524238018868</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>7.5897192007416052</v>
+        <v>9.999370831834133</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>21.673569349026682</v>
+        <v>25.090664135061601</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>35.484634385053234</v>
+        <v>40.005257190881593</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>51.074655463839406</v>
+        <v>56.935620883658196</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>72.679389439430082</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>80.513432618757903</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16653,7 +16642,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16668,14 +16657,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>45.548751974251395</v>
+        <v>50.317191361448984</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16690,7 +16679,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.269887669660939</v>
+        <v>37.357649019369674</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16698,7 +16687,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16713,7 +16702,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>29.318191600940459</v>
+        <v>33.236035365323517</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16721,7 +16710,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16736,7 +16725,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>24.878000087289131</v>
+        <v>28.601780673645852</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16744,7 +16733,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16759,21 +16748,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>15.121055640471935</v>
+        <v>18.344294236762746</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16781,23 +16770,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16831,16 +16820,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>444</v>
       </c>
@@ -16852,7 +16841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>443</v>
       </c>
@@ -16865,7 +16854,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>441</v>
       </c>
@@ -16886,24 +16875,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>442</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>2512.8275199999998</v>
+        <v>2680.3493546666668</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16913,13 +16902,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>445</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.42</v>
+        <v>7.9146666666666672</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -16927,10 +16916,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -16940,13 +16929,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -16956,7 +16945,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -16966,13 +16955,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>7.7740016137890926</v>
+        <v>8.2840821264192304</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -16980,10 +16969,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17001,7 +16990,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17015,15 +17004,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>188.91991685305965</v>
+        <v>189.7986141407483</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17037,15 +17026,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>177.54270189506965</v>
+        <v>179.19810274994853</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17059,15 +17048,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>166.85065037752827</v>
+        <v>169.1896443741573</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17081,15 +17070,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>156.80250009858199</v>
+        <v>159.74017204522013</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17103,15 +17092,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>147.35947376611023</v>
+        <v>150.81846563024092</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17125,15 +17114,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>138.48512935044263</v>
+        <v>142.39504868331454</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17147,15 +17136,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>130.14521944919861</v>
+        <v>134.44209105823094</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17169,15 +17158,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>122.30755912151605</v>
+        <v>126.93331696039232</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17191,15 +17180,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>114.94190168162382</v>
+        <v>119.84391813415631</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17213,15 +17202,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>108.01982197242555</v>
+        <v>113.15047189878439</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17243,7 +17232,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17265,7 +17254,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17287,7 +17276,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17309,7 +17298,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17331,7 +17320,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17353,7 +17342,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17375,7 +17364,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17397,7 +17386,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17419,7 +17408,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17441,7 +17430,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17463,7 +17452,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17485,7 +17474,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17507,7 +17496,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17529,7 +17518,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17551,7 +17540,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17573,7 +17562,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17595,7 +17584,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17617,7 +17606,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17639,7 +17628,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17661,13 +17650,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>2550.4188775163052</v>
+        <v>2720.4468026840591</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17675,30 +17664,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1181.3374159538025</v>
+        <v>1319.9442709294374</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>2632.7122905193592</v>
+        <v>2805.4541166046311</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17708,10 +17697,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>2632.7122905193592</v>
+        <v>2805.4541166046311</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17735,141 +17724,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>2320.0884246775549</v>
+        <v>2478.0096198326132</v>
       </c>
       <c r="C51" s="124">
-        <v>2473.167207375589</v>
+        <v>2638.747164143404</v>
       </c>
       <c r="D51" s="124">
-        <v>2573.4116924002578</v>
+        <v>2743.8678213108678</v>
       </c>
       <c r="E51" s="124">
-        <v>2656.2999649722678</v>
+        <v>2830.7100321127473</v>
       </c>
       <c r="F51" s="124">
-        <v>2741.696068748121</v>
+        <v>2920.1096419204482</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>2167.3569542617097</v>
+        <v>2319.432865832252</v>
       </c>
       <c r="C52" s="124">
-        <v>2437.2570765185151</v>
+        <v>2601.4561949129602</v>
       </c>
       <c r="D52" s="124">
-        <v>2633.0461449494678</v>
+        <v>2805.8024277647983</v>
       </c>
       <c r="E52" s="124">
-        <v>2807.2951361558858</v>
+        <v>2987.5438898789835</v>
       </c>
       <c r="F52" s="124">
-        <v>2999.2436793458351</v>
+        <v>3187.6416485402274</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>2007.0271960951834</v>
+        <v>2149.1550480489195</v>
       </c>
       <c r="C53" s="124">
-        <v>2395.9764601375809</v>
+        <v>2557.606887115363</v>
       </c>
       <c r="D53" s="124">
-        <v>2705.932441682487</v>
+        <v>2883.2330841461799</v>
       </c>
       <c r="E53" s="124">
-        <v>3001.5671768381071</v>
+        <v>3193.948936231825</v>
       </c>
       <c r="F53" s="124">
-        <v>3348.7284045621163</v>
+        <v>3558.9914760126399</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>1868.2167608434065</v>
+        <v>1998.3046556877625</v>
       </c>
       <c r="C54" s="124">
-        <v>2356.9817414063832</v>
+        <v>2515.2231979486937</v>
       </c>
       <c r="D54" s="124">
-        <v>2779.2194557307012</v>
+        <v>2962.8986783890232</v>
       </c>
       <c r="E54" s="124">
-        <v>3207.7525551693534</v>
+        <v>3418.102839637314</v>
       </c>
       <c r="F54" s="124">
-        <v>3741.533780102443</v>
+        <v>3986.0759139864931</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>1758.107875125437</v>
+        <v>1875.8506466119302</v>
       </c>
       <c r="C55" s="124">
-        <v>2323.387920872176</v>
+        <v>2477.8573668202175</v>
       </c>
       <c r="D55" s="124">
-        <v>2846.4604396038576</v>
+        <v>3037.6984601795966</v>
       </c>
       <c r="E55" s="124">
-        <v>3407.8678901723379</v>
+        <v>3640.7375673496058</v>
       </c>
       <c r="F55" s="124">
-        <v>4146.699500803451</v>
+        <v>4436.8882345197708</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>1674.9349111022073</v>
+        <v>1781.1878613734368</v>
       </c>
       <c r="C56" s="124">
-        <v>2295.9585520816736</v>
+        <v>2446.6344413628262</v>
       </c>
       <c r="D56" s="124">
-        <v>2904.9538058065068</v>
+        <v>3104.289470756918</v>
       </c>
       <c r="E56" s="124">
-        <v>3592.3916549285623</v>
+        <v>3850.8293723387992</v>
       </c>
       <c r="F56" s="124">
-        <v>4545.0466757254017</v>
+        <v>4890.4867342032267</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17879,7 +17868,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>-0.05</v>
@@ -17902,193 +17891,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>7.42</v>
+        <v>7.9146666666666672</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>7.42</v>
+        <v>7.9146666666666672</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>7.42</v>
+        <v>7.9146666666666672</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>7.42</v>
+        <v>7.9146666666666672</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>7.42</v>
+        <v>7.9146666666666672</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.850870572727354</v>
+        <v>7.317188001490047</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>7.3028890891512006</v>
+        <v>7.7918216837835566</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>7.5988959073521745</v>
+        <v>8.102227101574659</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>7.843652452554414</v>
+        <v>8.3586590289637499</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>8.0958142443899437</v>
+        <v>8.6226425692161026</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>6.399877616996922</v>
+        <v>6.8489348065064606</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>7.1968518984412357</v>
+        <v>7.681707085989796</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>7.7749874354786801</v>
+        <v>8.285110636648394</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>8.2895183789919145</v>
+        <v>8.8217657147045472</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>8.8563134252629077</v>
+        <v>9.4126241629861198</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>5.9264480655744576</v>
+        <v>6.3461301381015529</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>7.0749564754133427</v>
+        <v>7.5522267053156087</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>7.9902096572406425</v>
+        <v>8.5137516658384307</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>8.8631743622971602</v>
+        <v>9.4312486305626511</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>9.888289014699625</v>
+        <v>10.509164095756875</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>5.516561823335203</v>
+        <v>5.900691721651949</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>6.9598109627657072</v>
+        <v>7.4270740750162219</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>8.2066151366894466</v>
+        <v>8.7489921288535371</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>9.4720086316774346</v>
+        <v>10.09314123959804</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>11.048183939166716</v>
+        <v>11.770279912319561</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>5.1914269203127565</v>
+        <v>5.5391035345953714</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>6.8606134864646604</v>
+        <v>7.3167384213485587</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>8.4051676025343056</v>
+        <v>8.9698645828793726</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>10.062918980240532</v>
+        <v>10.750547952345761</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>12.244577095351776</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>13.101460581001874</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>4.9458297242694869</v>
+        <v>5.2595786325162903</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>6.7796187047672962</v>
+        <v>7.2245418399875572</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>8.5778896750877198</v>
+        <v>9.1664977757869881</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>10.607789777616704</v>
+        <v>11.370917309419585</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>13.420836116074724</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>14.440868415747032</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18105,7 +18094,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18120,14 +18109,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>9.888289014699625</v>
+        <v>10.509164095756875</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18142,7 +18131,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>8.2895183789919145</v>
+        <v>8.8217657147045472</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18150,7 +18139,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18165,7 +18154,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>7.7749874354786801</v>
+        <v>8.285110636648394</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18173,7 +18162,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18188,7 +18177,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>7.1968518984412357</v>
+        <v>7.681707085989796</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18196,7 +18185,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18211,21 +18200,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.9264480655744576</v>
+        <v>6.3461301381015529</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18233,23 +18222,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18279,7 +18268,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18289,7 +18278,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18302,7 +18291,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18314,7 +18303,7 @@
         <v>-22.73</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18334,7 +18323,7 @@
         <v>0.59360000000000002</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18343,7 +18332,7 @@
         <v>0.59360000000000002</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18360,10 +18349,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>29.903551346473133</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>33.823761875234659</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18388,7 +18377,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18410,7 +18399,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18432,7 +18421,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18443,7 +18432,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
@@ -18457,7 +18446,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18476,7 +18465,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18494,7 +18483,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18505,7 +18494,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18514,7 +18503,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18522,7 +18511,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18534,18 +18523,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18560,13 +18549,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>26.591820192356398</v>
+        <v>30.39095481513823</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18575,7 +18564,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18584,7 +18573,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18596,7 +18585,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18607,13 +18596,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>29.318191600940459</v>
+        <v>33.236035365323517</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18622,7 +18611,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18633,7 +18622,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18642,7 +18631,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18654,7 +18643,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18665,13 +18654,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>24.878000087289131</v>
+        <v>28.601780673645852</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18680,7 +18669,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18691,7 +18680,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18700,7 +18689,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18712,7 +18701,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18723,13 +18712,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.269887669660939</v>
+        <v>37.357649019369674</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18738,7 +18727,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18750,20 +18739,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>29.196067739707743</v>
+        <v>33.107875105915639</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18772,12 +18761,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18787,12 +18776,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18801,7 +18790,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18813,7 +18802,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18824,13 +18813,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>15.121055640471935</v>
+        <v>18.344294236762746</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18839,7 +18828,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18850,7 +18839,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18859,7 +18848,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18871,7 +18860,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18882,13 +18871,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>45.548751974251395</v>
+        <v>50.317191361448984</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18897,7 +18886,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18908,13 +18897,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>29.309951346473134</v>
+        <v>33.230161875234657</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -18937,7 +18926,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -18945,7 +18934,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -18958,7 +18947,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -18970,13 +18959,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.310620301790603</v>
+        <v>33.228136210024012</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18975,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -18994,7 +18983,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19004,7 +18993,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19016,7 +19005,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19026,7 +19015,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19039,10 +19028,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>-1.0370265985797507</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>-0.91468706241914388</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19051,12 +19040,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19066,7 +19055,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19079,49 +19068,49 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.94318367346938758</v>
+        <v>0.98374913197498015</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.681469149589338</v>
+        <v>12.997078146267045</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>11.624652823058726</v>
+        <v>13.980827278242025</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19132,18 +19121,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.60338887343606862</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.57927297102150221</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19156,24 +19145,24 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11252225662960313</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.15812491412146712</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
@@ -19182,7 +19171,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
@@ -19194,23 +19183,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>16.244831286867644</v>
+        <v>18.417579985626439</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>17.461949215913869</v>
+        <v>19.634697914672664</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19221,58 +19210,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.40423138170732364</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.40913023570596097</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.5297647716303417</v>
+        <v>1.5436720791879954</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>23.267184361562904</v>
+        <v>26.748970027985187</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>24.796949133193245</v>
+        <v>28.292642107173183</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19282,18 +19271,18 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>0.15397508374994073</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.14858548648061942</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>422</v>
       </c>
@@ -19302,7 +19291,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
@@ -19312,23 +19301,23 @@
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>21.008212246342826</v>
+        <v>23.818063885638704</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>22.440333461900007</v>
+        <v>25.250185101195886</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19338,19 +19327,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.23439581861974057</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.24009625632933929</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19358,7 +19347,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19366,7 +19355,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE014AD-B815-4A17-A03A-CE688C9B9E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349D4E1B-4DD4-436A-B380-30B2DFB33EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3866,29 +3866,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4306,7 +4306,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.73</v>
+        <v>22.47</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7697.6508800000001</v>
+        <v>7609.6003199999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4364,13 +4364,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15812491412146712</v>
+        <v>0.16267307080533766</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4570,22 +4570,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4597,13 +4597,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4623,13 +4623,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4658,13 +4658,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4680,13 +4680,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4750,13 +4750,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4772,7 +4772,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4794,22 +4794,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.20057023965412205</v>
+        <v>0.20289103459449018</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.6115266168059832E-2</v>
+        <v>2.6417445482866047E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4878,22 +4878,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4937,22 +4937,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4989,13 +4989,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5008,13 +5008,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5190,13 +5190,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5339,13 +5339,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5358,22 +5358,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5706,13 +5706,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5749,13 +5749,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5763,22 +5763,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5802,17 +5802,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5829,6 +5818,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.6115266168059832E-2</v>
+        <v>2.6417445482866047E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.6115266168059832E-2</v>
+        <v>2.6417445482866047E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14487,50 +14487,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.20057023965412205</v>
+        <v>0.20289103459449018</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14030254383269716</v>
+        <v>0.14192598225710756</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11834779391813621</v>
+        <v>0.11971719429280091</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.44286238141265244</v>
+        <v>0.44798673473562933</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.47741837831959455</v>
+        <v>0.48294257851376876</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.4390949982912189</v>
+        <v>0.4441757592861329</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.47988666381294759</v>
+        <v>0.48543942449792166</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.37249442001194005</v>
+        <v>0.37680454681225622</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.30672032764364598</v>
+        <v>0.31026938350423117</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.30489054863449466</v>
+        <v>0.30841843215229475</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.26573704522177555</v>
+        <v>0.26881188419630431</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14544,43 +14544,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.26956275782670985</v>
+        <v>-0.27268186405879463</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16342648161253059</v>
+        <v>0.16531748674022342</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15758054228616822</v>
+        <v>0.15940390414617728</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17070142832978158</v>
+        <v>0.17267661174614754</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7018178927854937E-2</v>
+        <v>1.7215095996001011E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11873752320656039</v>
+        <v>0.12011143313240399</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15275998071764979</v>
+        <v>0.15452756393912684</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4169574601439964E-2</v>
+        <v>8.514349936318337E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6903979100699353E-2</v>
+        <v>9.8025253447213898E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6218123937571982E-2</v>
+        <v>6.6984332759279536E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18300,7 +18300,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-22.73</v>
+        <v>-22.47</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18540,7 +18540,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>22.73</v>
+        <v>22.47</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19138,7 +19138,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>22.73</v>
+        <v>22.47</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19151,7 +19151,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15812491412146712</v>
+        <v>0.16267307080533766</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3BF4ED-5899-49D5-B0D6-788851BB5C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6DBAE6-7A79-4D59-A460-89F66BBF1596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3865,29 +3865,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.47</v>
+        <v>22.531199999999998</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7609.6003199999996</v>
+        <v>7630.3260671999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,13 +4363,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16267307080533766</v>
+        <v>0.16159611874486934</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4569,22 +4569,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4596,13 +4596,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4622,13 +4622,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4657,13 +4657,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4749,13 +4749,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4793,22 +4793,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.20289103459449018</v>
+        <v>0.20233993517159291</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.6417445482866047E-2</v>
+        <v>2.6345689532736829E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4877,22 +4877,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4936,22 +4936,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4988,13 +4988,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5007,13 +5007,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5144,13 +5144,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5189,13 +5189,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5338,13 +5338,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5357,22 +5357,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5705,13 +5705,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5762,22 +5762,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5801,6 +5801,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5817,17 +5828,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13290,12 +13290,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.6417445482866047E-2</v>
+        <v>2.6345689532736829E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.6417445482866047E-2</v>
+        <v>2.6345689532736829E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14489,50 +14489,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.20289103459449018</v>
+        <v>0.20233993517159291</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14192598225710756</v>
+        <v>0.14154047815106194</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11971719429280091</v>
+        <v>0.11939201444038651</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.44798673473562933</v>
+        <v>0.44676989816386126</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.48294257851376876</v>
+        <v>0.48163079370847467</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.4441757592861329</v>
+        <v>0.44296927421350868</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.48543942449792166</v>
+        <v>0.48412085767594709</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.37680454681225622</v>
+        <v>0.37578105768318587</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.31026938350423117</v>
+        <v>0.30942661941397148</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.30841843215229475</v>
+        <v>0.30758069567808477</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.26881188419630431</v>
+        <v>0.2680817283540583</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14546,43 +14546,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.27268186405879463</v>
+        <v>-0.27194119644764214</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16531748674022342</v>
+        <v>0.16486844584632956</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15940390414617728</v>
+        <v>0.15897092592336864</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17267661174614754</v>
+        <v>0.17220758175045869</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7215095996001011E-2</v>
+        <v>1.7168335775730664E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12011143313240399</v>
+        <v>0.11978518243525058</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15452756393912684</v>
+        <v>0.15410783099489508</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.514349936318337E-2</v>
+        <v>8.491222973879467E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8025253447213898E-2</v>
+        <v>9.7758993970977856E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6984332759279536E-2</v>
+        <v>6.6802387671362873E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18302,7 +18302,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.47</v>
+        <v>-22.531199999999998</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.47</v>
+        <v>22.531199999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.47</v>
+        <v>22.531199999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19153,7 +19153,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16267307080533766</v>
+        <v>0.16159611874486934</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8257E0E4-CC2F-4C2A-B106-C998B942034C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD877A6-9AB3-44C9-A850-7553BBFC5962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3879,29 +3879,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4319,7 +4319,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.531199999999998</v>
+        <v>21.92</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7630.3260671999997</v>
+        <v>7423.3395200000014</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4377,13 +4377,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16159611874486934</v>
+        <v>0.17253311267270033</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4583,22 +4583,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,13 +4610,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4636,13 +4636,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4671,13 +4671,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4693,13 +4693,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4763,13 +4763,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4785,7 +4785,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4807,22 +4807,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.20233993517159291</v>
+        <v>0.20798182241506358</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.6345689532736829E-2</v>
+        <v>2.708029197080292E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5016,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5068,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,13 +5087,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5215,13 +5215,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5260,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5409,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5428,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5776,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5819,13 +5819,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5833,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5872,6 +5872,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5888,17 +5899,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.6345689532736829E-2</v>
+        <v>2.708029197080292E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.6345689532736829E-2</v>
+        <v>2.708029197080292E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14560,50 +14560,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.20233993517159291</v>
+        <v>0.20798182241506358</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14154047815106194</v>
+        <v>0.1454870812644711</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11939201444038651</v>
+        <v>0.12272104725178996</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.44676989816386126</v>
+        <v>0.4592272778060944</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.48163079370847467</v>
+        <v>0.49506020708049192</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.44296927421350868</v>
+        <v>0.45532068025362249</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.48412085767594709</v>
+        <v>0.49761970202866324</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.37578105768318587</v>
+        <v>0.38625904045946152</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.30942661941397148</v>
+        <v>0.31805442734215661</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.30758069567808477</v>
+        <v>0.31615703332399919</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.2680817283540583</v>
+        <v>0.27555670793298165</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14617,43 +14617,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.27194119644764214</v>
+        <v>-0.27952379039238662</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16486844584632956</v>
+        <v>0.1694655076210228</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15897092592336864</v>
+        <v>0.16340354590166986</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17220758175045869</v>
+        <v>0.17700928220510651</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7168335775730664E-2</v>
+        <v>1.7647044116338623E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11978518243525058</v>
+        <v>0.12312517803308017</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15410783099489508</v>
+        <v>0.15840485226789139</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.491222973879467E-2</v>
+        <v>8.7279855414723093E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7758993970977856E-2</v>
+        <v>0.1004848286933803</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6802387671362873E-2</v>
+        <v>6.8665052787454869E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18373,7 +18373,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.531199999999998</v>
+        <v>-21.92</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.531199999999998</v>
+        <v>21.92</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19211,7 +19211,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.531199999999998</v>
+        <v>21.92</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16159611874486934</v>
+        <v>0.17253311267270033</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD877A6-9AB3-44C9-A850-7553BBFC5962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E4F4F7-0AFA-4730-AA2E-20240F43A247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2480,7 +2480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2498,6 +2498,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3146,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3818,36 +3819,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3862,10 +3840,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3877,6 +3851,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4377,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4583,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,19 +4626,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>2626.9774440472893</v>
       </c>
@@ -4636,19 +4652,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>578</v>
       </c>
@@ -4661,7 +4677,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-632.31340126010366</v>
       </c>
@@ -4671,19 +4687,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4693,19 +4709,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4720,7 +4736,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-496</v>
       </c>
@@ -4735,7 +4751,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-496</v>
       </c>
@@ -4753,7 +4769,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
@@ -4763,19 +4779,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-532.74436101182232</v>
       </c>
@@ -4785,19 +4801,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4807,28 +4823,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>1080</v>
       </c>
@@ -4841,7 +4857,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>1543.9196817753634</v>
       </c>
@@ -4880,10 +4896,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4905,11 +4921,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.23497655430253014</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.14829290723071617</v>
       </c>
@@ -4919,11 +4935,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.32112750263435197</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.31608589804149556</v>
       </c>
@@ -4933,11 +4949,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>2.4851905363915479</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>2.4851905363915479</v>
       </c>
@@ -4957,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,19 +5103,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>10547</v>
       </c>
@@ -5125,7 +5141,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.95241105291674188</v>
       </c>
@@ -5134,7 +5150,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>4.0148803043206254</v>
       </c>
@@ -5148,7 +5164,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>162</v>
       </c>
@@ -5161,7 +5177,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>-372.31656312939253</v>
       </c>
@@ -5192,7 +5208,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>625.79999999999995</v>
       </c>
@@ -5215,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5790,13 +5806,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5819,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6014,325 +6030,325 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>8699</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>8953</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>9003</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>8696</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>8040</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>7794</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>5770.692</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>5425.1289999999999</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>5017.22</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>4570.058</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>4129</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>4209</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>4130</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>3968</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>3579</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>3427</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>2308.6060000000002</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>2101.982</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>1993.327</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>1843.164</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <f>296+497+578+C7</f>
         <v>2634</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <f>322+608+624+D7</f>
         <v>2844</v>
       </c>
-      <c r="E6" s="334"/>
-      <c r="F6" s="334"/>
-      <c r="G6" s="334"/>
-      <c r="H6" s="334"/>
-      <c r="I6" s="334"/>
-      <c r="J6" s="334"/>
-      <c r="K6" s="334"/>
-      <c r="L6" s="334"/>
-      <c r="M6" s="334"/>
+      <c r="E6" s="321"/>
+      <c r="F6" s="321"/>
+      <c r="G6" s="321"/>
+      <c r="H6" s="321"/>
+      <c r="I6" s="321"/>
+      <c r="J6" s="321"/>
+      <c r="K6" s="321"/>
+      <c r="L6" s="321"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <f>369+894</f>
         <v>1263</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <f>359+931</f>
         <v>1290</v>
       </c>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
-      <c r="G7" s="335"/>
-      <c r="H7" s="335"/>
-      <c r="I7" s="335"/>
-      <c r="J7" s="335"/>
-      <c r="K7" s="335"/>
-      <c r="L7" s="335"/>
-      <c r="M7" s="335"/>
+      <c r="E7" s="322"/>
+      <c r="F7" s="322"/>
+      <c r="G7" s="322"/>
+      <c r="H7" s="322"/>
+      <c r="I7" s="322"/>
+      <c r="J7" s="322"/>
+      <c r="K7" s="322"/>
+      <c r="L7" s="322"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334"/>
-      <c r="D8" s="334"/>
-      <c r="E8" s="334"/>
-      <c r="F8" s="334"/>
-      <c r="G8" s="334"/>
-      <c r="H8" s="334"/>
-      <c r="I8" s="334"/>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="C8" s="321"/>
+      <c r="D8" s="321"/>
+      <c r="E8" s="321"/>
+      <c r="F8" s="321"/>
+      <c r="G8" s="321"/>
+      <c r="H8" s="321"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>496</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>423</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>422</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>415</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>394</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>390</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>350.07299999999998</v>
       </c>
-      <c r="J12" s="334">
+      <c r="J12" s="321">
         <v>345.82</v>
       </c>
-      <c r="K12" s="334">
+      <c r="K12" s="321">
         <v>331.22500000000002</v>
       </c>
-      <c r="L12" s="334">
+      <c r="L12" s="321">
         <v>299.10300000000001</v>
       </c>
-      <c r="M12" s="334"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334"/>
-      <c r="D13" s="334"/>
-      <c r="E13" s="334"/>
-      <c r="F13" s="334"/>
-      <c r="G13" s="334"/>
-      <c r="H13" s="334"/>
-      <c r="I13" s="334"/>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="C13" s="321"/>
+      <c r="D13" s="321"/>
+      <c r="E13" s="321"/>
+      <c r="F13" s="321"/>
+      <c r="G13" s="321"/>
+      <c r="H13" s="321"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>210</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>260</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>392</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>212</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>299</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>283</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>244.68100000000001</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>616.30100000000004</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>345.72699999999998</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>382.24</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>-2075</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>1258</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>1213</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>1314</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>131</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>914</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>1175.893</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>647.90800000000002</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>745.93299999999999</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>509.72399999999999</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>-410</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>202</v>
       </c>
-      <c r="E16" s="334"/>
-      <c r="F16" s="334"/>
-      <c r="G16" s="334"/>
-      <c r="H16" s="334"/>
-      <c r="I16" s="334"/>
-      <c r="J16" s="334"/>
-      <c r="K16" s="334"/>
-      <c r="L16" s="334"/>
-      <c r="M16" s="334"/>
+      <c r="E16" s="321"/>
+      <c r="F16" s="321"/>
+      <c r="G16" s="321"/>
+      <c r="H16" s="321"/>
+      <c r="I16" s="321"/>
+      <c r="J16" s="321"/>
+      <c r="K16" s="321"/>
+      <c r="L16" s="321"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6344,181 +6360,181 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>578</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>624</v>
       </c>
-      <c r="E19" s="334"/>
-      <c r="F19" s="334"/>
-      <c r="G19" s="334"/>
-      <c r="H19" s="334"/>
-      <c r="I19" s="334"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334">
+      <c r="C20" s="321">
         <v>728</v>
       </c>
-      <c r="D20" s="334">
+      <c r="D20" s="321">
         <v>728</v>
       </c>
-      <c r="E20" s="334">
+      <c r="E20" s="321">
         <v>650</v>
       </c>
-      <c r="F20" s="334">
+      <c r="F20" s="321">
         <v>426</v>
       </c>
-      <c r="G20" s="334">
+      <c r="G20" s="321">
         <v>388</v>
       </c>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334">
+      <c r="C21" s="321">
         <v>259</v>
       </c>
-      <c r="D21" s="334">
+      <c r="D21" s="321">
         <v>259</v>
       </c>
-      <c r="E21" s="334">
+      <c r="E21" s="321">
         <v>169</v>
       </c>
-      <c r="F21" s="334">
+      <c r="F21" s="321">
         <v>340</v>
       </c>
-      <c r="G21" s="334">
+      <c r="G21" s="321">
         <v>411</v>
       </c>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>1741</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>1850</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>1976</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>1998</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>2018</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>2017</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>1880.4179999999999</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>1855.5889999999999</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>1719.2370000000001</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>1244.0509999999999</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-970</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-686</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-548</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-200</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-741</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-3</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-379.27600000000001</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-1146.8119999999999</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-210.124</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-138.858</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-916</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-1005</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-1562</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-1682</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-1314</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-1959</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-1515.146</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-853.69399999999996</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-1407.0119999999999</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-1141.079</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6552,150 +6568,150 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>676</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>709</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>655</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>722</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>672</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>670</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>232.98599999999999</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>241.727</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>223.029</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>234.78200000000001</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>0</v>
       </c>
-      <c r="D29" s="334"/>
-      <c r="E29" s="334"/>
-      <c r="F29" s="334"/>
-      <c r="G29" s="334"/>
-      <c r="H29" s="334"/>
-      <c r="I29" s="334"/>
-      <c r="J29" s="334"/>
-      <c r="K29" s="334"/>
-      <c r="L29" s="334"/>
-      <c r="M29" s="334"/>
+      <c r="D29" s="321"/>
+      <c r="E29" s="321"/>
+      <c r="F29" s="321"/>
+      <c r="G29" s="321"/>
+      <c r="H29" s="321"/>
+      <c r="I29" s="321"/>
+      <c r="J29" s="321"/>
+      <c r="K29" s="321"/>
+      <c r="L29" s="321"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>16447</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>12939</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>13373</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>12899</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>12618</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>11885</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>9989.6569999999992</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>9853.2479999999996</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>8795.61</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>8213.1530000000002</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>11074</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>-2565</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>-3351</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>-2625</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>-2285</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>-736</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>-1816.921</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>-1523.874</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>-792.01499999999999</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>-166.49100000000001</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>0</v>
       </c>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="334"/>
-      <c r="G32" s="334"/>
-      <c r="H32" s="334"/>
-      <c r="I32" s="334"/>
-      <c r="J32" s="334"/>
-      <c r="K32" s="334"/>
-      <c r="L32" s="334"/>
-      <c r="M32" s="334"/>
+      <c r="D32" s="321"/>
+      <c r="E32" s="321"/>
+      <c r="F32" s="321"/>
+      <c r="G32" s="321"/>
+      <c r="H32" s="321"/>
+      <c r="I32" s="321"/>
+      <c r="J32" s="321"/>
+      <c r="K32" s="321"/>
+      <c r="L32" s="321"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6722,47 +6738,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>8699</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>8953</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>9003</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>8696</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>8040</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>7794</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>5770.692</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>5425.1289999999999</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>5017.22</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>4570.058</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6771,47 +6787,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-4129</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-4209</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-4130</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-3968</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-3579</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-3427</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-2308.6060000000002</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-2101.982</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-1993.327</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-1843.164</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6820,47 +6836,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>4570</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>4744</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>4873</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>4728</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>4461</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>4367</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>3462.0859999999998</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>3323.1469999999999</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>3023.893</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>2726.8940000000002</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6869,47 +6885,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-2634</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-2844</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -6918,47 +6934,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-1263</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-1290</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -6967,47 +6983,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-1371</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-1554</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7016,47 +7032,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7065,47 +7081,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>1936</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>1900</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>4873</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>4728</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>4461</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>4367</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>3462.0859999999998</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>3323.1469999999999</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>3023.893</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>2726.8940000000002</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7212,47 +7228,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-210</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-260</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-392</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-212</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-299</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-283</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-244.68100000000001</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-616.30100000000004</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-345.72699999999998</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-382.24</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7261,47 +7277,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>-2075</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>1258</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>1213</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>1314</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>131</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>914</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>1175.893</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>647.90800000000002</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>745.93299999999999</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>509.72399999999999</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7310,47 +7326,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-202</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7364,47 +7380,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-496</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-423</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-422</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-415</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-394</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-390</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-350.07299999999998</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>-345.82</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>-331.22500000000002</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>-299.10300000000001</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7413,47 +7429,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7669,47 +7685,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-578</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-624</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7718,47 +7734,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-728</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-728</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-650</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-426</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-388</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7767,47 +7783,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>-259</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>-259</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>-169</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>-340</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>-411</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7816,47 +7832,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-145</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>159</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>-134</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>116</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>-37</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>55</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>-14.004000000000133</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>-144.91699999999992</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>102.10100000000011</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>-35.885999999999967</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8238,115 +8254,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>676</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>709</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>655</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>722</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>672</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>670</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>16447</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>12939</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>13373</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>12899</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>12618</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>11885</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>9989.6569999999992</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>9853.2479999999996</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>8795.61</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>8213.1530000000002</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8355,47 +8371,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>11074</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>-2565</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>-3351</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>-2625</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>-2285</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>-736</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>-1816.921</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>-1523.874</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>-792.01499999999999</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>-166.49100000000001</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9477,11 +9493,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-580.33551679999994</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-534.31656312939253</v>
       </c>
@@ -9509,8 +9525,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>534.31656312939253</v>
       </c>
@@ -9814,54 +9830,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>8837.75</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>8699</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>8953</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>9003</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>8696</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>8040</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>7794</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>5770.692</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>5425.1289999999999</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>5017.22</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>4570.058</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9871,52 +9887,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-4748.2725559527107</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5392</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-5499</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-4130</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-3968</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-3579</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-3427</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-2308.6060000000002</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-2101.982</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-1993.327</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-1843.164</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9926,52 +9942,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>4089.4774440472893</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>3307</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>3454</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>4873</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>4728</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>4461</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>4367</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>3462.0859999999998</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>3323.1469999999999</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>3023.893</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>2726.8940000000002</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9981,52 +9997,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-1462.5</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1371</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-1554</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10036,54 +10052,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>2626.9774440472893</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>1936</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>1900</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>4873</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>4728</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>4461</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>4367</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>3462.0859999999998</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>3323.1469999999999</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>3023.893</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>2726.8940000000002</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10093,52 +10109,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>578</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>578</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>624</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10148,52 +10164,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-632.31340126010366</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-728</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-728</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-650</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-426</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-388</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>0</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>0</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10203,54 +10219,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10260,52 +10276,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-496</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-496</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-423</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-422</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-415</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-394</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-390</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-350.07299999999998</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>-345.82</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>-331.22500000000002</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>-299.10300000000001</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10315,52 +10331,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>2076.6640427871857</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1290</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>1373</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>3801</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>3887</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>3679</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>3977</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>3112.0129999999999</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>2977.3269999999998</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>2692.6680000000001</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>2427.7910000000002</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10370,52 +10386,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-532.74436101182232</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-210</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-260</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-392</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-212</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-299</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-283</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-244.68100000000001</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-616.30100000000004</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-345.72699999999998</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-382.24</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10425,54 +10441,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-202</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10482,54 +10498,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>1543.9196817753634</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>1080</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>911</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>3409</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>3675</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>3380</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>3694</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>2867.3319999999999</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>2361.0259999999998</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>2346.9410000000003</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>2045.5510000000002</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10539,7 +10555,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10548,24 +10564,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10573,71 +10589,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>1543.9196817753634</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>1080</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>911</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>3409</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>3675</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>3380</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>3694</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>2867.3319999999999</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>2361.0259999999998</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>2346.9410000000003</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>2045.5510000000002</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10710,54 +10726,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-4109.1377805440734</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-4129</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-4209</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-4130</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-3968</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-3579</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-3427</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-2308.6060000000002</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-2101.982</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-1993.327</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-1843.164</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10767,54 +10783,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-639.13477540863767</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-1263</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-1290</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>0</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>0</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>0</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>0</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>0</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>0</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>0</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10824,54 +10840,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-4748.2725559527107</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-5392</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-5499</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-4130</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-3968</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-3579</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-3427</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-2308.6060000000002</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-2101.982</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-1993.327</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-1843.164</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11077,54 +11093,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:H33)</f>
         <v>-1462.5</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-1371</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-1554</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>0</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>0</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>0</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>0</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>0</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>0</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>0</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>0</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11134,7 +11150,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
@@ -11143,47 +11159,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>0</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11193,54 +11209,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-1462.5</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-1371</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-1554</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11534,52 +11550,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-496</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-496</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-423</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-422</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-415</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-394</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-390</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-350.07299999999998</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>-345.82</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>-331.22500000000002</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>-299.10300000000001</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11589,52 +11605,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11644,54 +11660,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11701,52 +11717,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-496</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-496</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-423</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-422</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-415</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-394</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-390</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-350.07299999999998</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>-345.82</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>-331.22500000000002</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>-299.10300000000001</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11893,52 +11909,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -11948,52 +11964,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12003,52 +12019,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12058,52 +12074,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12113,53 +12129,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-3305</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>41</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>-2846</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>-2787</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-3637</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>-2780</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>-1691.4389999999999</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-1713.1179999999999</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-1601.0080000000003</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-1535.8270000000002</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12169,52 +12185,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-3305</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>41</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>-2846</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>-2787</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>-3637</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>-2780</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>-1691.4389999999999</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-1713.1179999999999</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-1601.0080000000003</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-1535.8270000000002</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13589,54 +13605,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>27521</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>27521</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>10374</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>10022</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>10274</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>10333</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>11149</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>8172.735999999999</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>8329.3739999999998</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>8003.5950000000003</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>8046.6620000000003</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13646,54 +13662,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>676</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>709</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>655</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>722</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>672</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>670</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13703,54 +13719,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>0</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>0</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>0</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>0</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13760,54 +13776,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>16447</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>16447</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>12939</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>13373</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>12899</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>12618</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>11885</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>9989.6569999999992</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>9853.2479999999996</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>8795.61</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>8213.1530000000002</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13817,54 +13833,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>11074</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>11074</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>-2565</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>-3351</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>-2625</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>-2285</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>-736</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>-1816.921</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>-1523.874</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>-792.01499999999999</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>-166.49100000000001</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15362,7 +15378,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15401,7 +15417,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>1543.9196817753634</v>
       </c>
@@ -15433,7 +15449,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>20585.595757004845</v>
       </c>
@@ -15441,17 +15457,17 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>10547</v>
       </c>
@@ -15459,15 +15475,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>-372.31656312939253</v>
       </c>
@@ -15475,15 +15491,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>625.79999999999995</v>
       </c>
@@ -15491,15 +15507,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>10292.079193875452</v>
       </c>
@@ -15566,7 +15582,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15576,7 +15592,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15590,10 +15606,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15611,7 +15627,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15633,7 +15649,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15655,7 +15671,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15675,9 +15691,19 @@
         <f t="shared" si="1"/>
         <v>1299.4088323948902</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15697,9 +15723,19 @@
         <f t="shared" si="1"/>
         <v>1226.8350773573889</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15719,9 +15755,19 @@
         <f t="shared" si="1"/>
         <v>1158.3146654932873</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15743,7 +15789,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15765,7 +15811,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15787,7 +15833,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15809,7 +15855,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15831,7 +15877,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15853,7 +15899,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15875,11 +15921,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15895,13 +15941,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15917,13 +15973,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15939,9 +16005,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -15963,7 +16039,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -15985,7 +16061,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16007,7 +16083,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16029,7 +16105,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16051,7 +16127,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16073,7 +16149,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16095,7 +16171,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16117,7 +16193,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16139,7 +16215,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16161,7 +16237,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16183,11 +16259,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16203,13 +16279,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16225,13 +16311,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16247,13 +16343,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16269,9 +16375,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16293,7 +16409,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16304,11 +16420,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16318,7 +16434,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>21546.424259471285</v>
@@ -16345,7 +16461,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16367,7 +16483,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16388,14 +16504,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>16505.921872174516</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>19642.910127301682</v>
       </c>
       <c r="D58" s="123">
@@ -16407,16 +16523,26 @@
       <c r="F58" s="123">
         <v>27333.73532083226</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>15347.362003280659</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>19317.395287097537</v>
       </c>
       <c r="D59" s="123">
@@ -16428,16 +16554,26 @@
       <c r="F59" s="123">
         <v>30613.825499722654</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>14406.891789847168</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>19030.418556472443</v>
       </c>
       <c r="D60" s="123">
@@ -16449,16 +16585,26 @@
       <c r="F60" s="123">
         <v>34076.150355479913</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>13679.863491555012</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>18790.620516452815</v>
       </c>
       <c r="D61" s="123">
@@ -16470,26 +16616,56 @@
       <c r="F61" s="123">
         <v>37559.873600067469</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.05</v>
@@ -16861,6 +17037,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16963,7 +17209,7 @@
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>2680.3493546666668</v>
       </c>
@@ -16971,8 +17217,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18429,7 +18675,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>1936</v>
       </c>
@@ -18437,11 +18683,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for Sirius XM(SIRI). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18454,7 +18700,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>1080</v>
       </c>
@@ -18462,8 +18708,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18476,7 +18722,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>1543.9196817753634</v>
       </c>
@@ -18484,8 +18730,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18495,8 +18741,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18509,8 +18755,8 @@
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18528,8 +18774,8 @@
         <v>1.1498217877581318E-4</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18546,8 +18792,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.25742105972151286</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18564,8 +18810,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.3351523510141251</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18591,21 +18837,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18619,8 +18865,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18634,8 +18880,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18655,8 +18901,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18666,8 +18912,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18681,8 +18927,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18692,8 +18938,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18713,8 +18959,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18724,8 +18970,8 @@
         <v>-0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18739,8 +18985,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18750,8 +18996,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18771,8 +19017,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18782,8 +19028,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18797,8 +19043,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18809,8 +19055,8 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18872,8 +19118,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18883,8 +19129,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18898,8 +19144,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18909,8 +19155,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -18930,8 +19176,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -18941,8 +19187,8 @@
         <v>5.5E-2</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -18956,8 +19202,8 @@
         <f>Market_currency</f>
         <v>USD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -18967,8 +19213,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E4F4F7-0AFA-4730-AA2E-20240F43A247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE211E1-AFBF-4868-BF2F-EC0741001910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,29 +3895,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4335,7 +4335,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>21.92</v>
+        <v>21.84</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7423.3395200000014</v>
+        <v>7396.2470400000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4393,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17253311267270033</v>
+        <v>0.17399519621605997</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4599,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4626,13 +4626,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4652,13 +4652,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4687,13 +4687,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4709,13 +4709,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4779,13 +4779,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4801,7 +4801,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4823,22 +4823,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.20798182241506358</v>
+        <v>0.20874366059240815</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.708029197080292E-2</v>
+        <v>2.7179487179487181E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5032,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5084,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5103,13 +5103,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5231,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5276,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5425,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5444,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5792,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5835,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5849,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5888,17 +5888,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5915,6 +5904,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.708029197080292E-2</v>
+        <v>2.7179487179487181E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.708029197080292E-2</v>
+        <v>2.7179487179487181E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14576,50 +14576,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.20798182241506358</v>
+        <v>0.20874366059240815</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1454870812644711</v>
+        <v>0.14602000097606258</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.12272104725178996</v>
+        <v>0.12317057489740094</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.4592272778060944</v>
+        <v>0.46090942900684939</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.49506020708049192</v>
+        <v>0.49687361443243516</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.45532068025362249</v>
+        <v>0.45698852157323289</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.49761970202866324</v>
+        <v>0.49944248481997705</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.38625904045946152</v>
+        <v>0.38767390873953284</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.31805442734215661</v>
+        <v>0.31921946187454553</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.31615703332399919</v>
+        <v>0.31731511769514942</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.27555670793298165</v>
+        <v>0.2765660731635054</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14633,43 +14633,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-0.27952379039238662</v>
+        <v>-0.2805476870604906</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1694655076210228</v>
+        <v>0.17008626039619143</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16340354590166986</v>
+        <v>0.16400209368885549</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17700928220510651</v>
+        <v>0.17765766785420947</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7647044116338623E-2</v>
+        <v>1.7711685303577963E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12312517803308017</v>
+        <v>0.12357618601122333</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15840485226789139</v>
+        <v>0.15898508982198625</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7279855414723093E-2</v>
+        <v>8.759956184481367E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1004848286933803</v>
+        <v>0.10085290498896045</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8665052787454869E-2</v>
+        <v>6.8916573127335665E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18619,7 +18619,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.92</v>
+        <v>-21.84</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.92</v>
+        <v>21.84</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.92</v>
+        <v>21.84</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17253311267270033</v>
+        <v>0.17399519621605997</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/SIRI_Valuation.xlsx
+++ b/financial_models/opportunities/SIRI_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C692101-58F4-4CDD-941A-57CEB4AD57AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1994DD1D-4C28-914A-B0DC-D634DC7059E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2510,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3891,30 +3902,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3929,7 +3940,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4218,16 +4229,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4244,7 +4255,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4258,7 +4269,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>414</v>
       </c>
@@ -4267,7 +4278,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4275,7 +4286,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4284,7 +4295,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4294,7 +4305,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4304,17 +4315,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>417</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>416</v>
       </c>
@@ -4326,17 +4337,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.84</v>
+        <v>22.26</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>415</v>
       </c>
@@ -4346,13 +4357,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>419</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7396.2470400000002</v>
+        <v>7538.4825600000013</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4360,7 +4371,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>418</v>
       </c>
@@ -4374,7 +4385,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4384,27 +4395,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4419,7 +4430,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4432,7 +4443,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>433</v>
       </c>
@@ -4440,7 +4451,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>434</v>
       </c>
@@ -4448,7 +4459,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4464,7 +4475,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (USD) :</v>
@@ -4478,14 +4489,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17399519621605997</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.16639888307370398</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>432</v>
       </c>
@@ -4504,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>424</v>
       </c>
@@ -4523,7 +4534,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>425</v>
       </c>
@@ -4542,7 +4553,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>426</v>
       </c>
@@ -4561,7 +4572,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>427</v>
       </c>
@@ -4580,11 +4591,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4594,25 +4605,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4621,16 +4632,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4643,20 +4654,20 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4682,16 +4693,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4704,16 +4715,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4728,7 +4739,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4743,7 +4754,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4756,12 +4767,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4774,16 +4785,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4796,8 +4807,8 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4805,7 +4816,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4818,25 +4829,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4849,7 +4860,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4862,23 +4873,23 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.20874366059240815</v>
+        <v>0.20480510095858911</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.7179487179487181E-2</v>
+        <v>2.6666666666666665E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4888,7 +4899,7 @@
         <v>0.130205090311977</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4899,7 +4910,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4912,7 +4923,7 @@
         <v>0.1164890735055084</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4926,7 +4937,7 @@
         <v>0.14829290723071617</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4940,7 +4951,7 @@
         <v>0.31608589804149556</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4954,7 +4965,7 @@
         <v>2.4851905363915479</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4964,34 +4975,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>430</v>
       </c>
@@ -5000,7 +5011,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>429</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5018,34 +5029,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5053,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5066,7 +5077,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5076,38 +5087,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5120,7 +5131,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5133,7 +5144,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5142,7 +5153,7 @@
         <v>0.95241105291674188</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5151,12 +5162,12 @@
         <v>4.0148803043206254</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5169,7 +5180,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5182,7 +5193,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5195,12 +5206,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5213,7 +5224,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5226,16 +5237,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>448</v>
       </c>
@@ -5248,7 +5259,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5261,7 +5272,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5271,16 +5282,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5297,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5319,7 +5330,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5341,7 +5352,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5363,7 +5374,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5385,7 +5396,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5407,7 +5418,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5420,16 +5431,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5439,30 +5450,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5471,7 +5482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5480,7 +5491,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5493,7 +5504,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5506,7 +5517,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5515,7 +5526,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5525,7 +5536,7 @@
         <v>0.98374913197498015</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5535,7 +5546,7 @@
         <v>12.997078146267045</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5548,7 +5559,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>415</v>
       </c>
@@ -5561,7 +5572,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5570,12 +5581,12 @@
         <v>0.57927297102150221</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5584,7 +5595,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5594,7 +5605,7 @@
         <v>1.2171179290462264</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5604,7 +5615,7 @@
         <v>18.417579985626439</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5617,7 +5628,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>415</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5639,12 +5650,12 @@
         <v>0.40913023570596097</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5653,7 +5664,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5663,7 +5674,7 @@
         <v>1.5436720791879954</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5673,7 +5684,7 @@
         <v>26.748970027985187</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5686,7 +5697,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>415</v>
       </c>
@@ -5699,7 +5710,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5708,12 +5719,12 @@
         <v>0.14858548648061942</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>422</v>
       </c>
@@ -5722,7 +5733,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5732,7 +5743,7 @@
         <v>1.4321212155571821</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5742,7 +5753,7 @@
         <v>23.818063885638704</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5755,7 +5766,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>415</v>
       </c>
@@ -5768,7 +5779,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5777,7 +5788,7 @@
         <v>0.24009625632933929</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5787,21 +5798,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5810,80 +5821,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight